--- a/.cursor/scratch/tax_turbo_parts/Personal Income 2025 — Mercury 8291.xlsx
+++ b/.cursor/scratch/tax_turbo_parts/Personal Income 2025 — Mercury 8291.xlsx
@@ -667,7 +667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -678,7 +678,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ASK — remaining Mercury 8291 questions. Q6 David Aaron consultant fee and Q8 Koziol/Ariadne pass-through LOCKED 2026-09-20. Not tax advice.</t>
+          <t>ASK — remaining Mercury 8291 questions. Q6 consultant, Q7 Wise expertise write-ups, Q8 pass-through LOCKED 2026-09-20. Not tax advice.</t>
         </is>
       </c>
     </row>
@@ -768,14 +768,14 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>7. Wise $334.17 (7/9) and $658.63 (10/30)</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Who / what? Dec $565.75 was reimbursed by EOEB (locked net $0). These two were not.</t>
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>7. Wise $334.17 (7/9) and $658.63 (10/30) — LOCKED expertise write-ups</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>CONFIRMED 2026-09-20: business expenses (expertise write-ups). Booked EPGC Consultant Fees July $334.17 + October $658.63 = $992.80. Not COGS. Distinct from Dec Wise $565.75 reimbursed by EOEB (still not P&amp;L).</t>
         </is>
       </c>
     </row>
@@ -928,6 +928,18 @@
       <c r="B24" s="7" t="inlineStr">
         <is>
           <t>$150,000 IN 10/20 + $150,000 OUT 10/21 LOCKED pass-through — not P&amp;L</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Wise expertise write-ups</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>$334.17 (7/9) + $658.63 (10/30) = $992.80 → EPGC Consultant Fees expense. Dec $565.75 still reimbursed / not P&amp;L.</t>
         </is>
       </c>
     </row>
@@ -963,7 +975,7 @@
     <row r="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>Mercury Checking 8291 — EPGC LLC (Choice Financial) 2025. 64 unique cash transactions. Coinbase ACH = investment. Newstar = jewelry COGS on intaglios/gems/scarabs. BoA 9922 draws and Koziol/Ariadne $150k are LOCKED not-P&amp;L (pass-through / owner transfer). David Aaron $13,595 is LOCKED EPGC Consultant (June). Not tax advice.</t>
+          <t>Mercury Checking 8291 — EPGC LLC (Choice Financial) 2025. 64 unique cash transactions. Coinbase ACH = investment. Newstar = jewelry COGS on intaglios/gems/scarabs. BoA 9922 draws and Koziol/Ariadne $150k are LOCKED not-P&amp;L (pass-through / owner transfer). David Aaron $13,595 is LOCKED EPGC Consultant (June). Wise $334.17 + $658.63 are LOCKED EPGC Consultant Fees (expertise write-ups). Not tax advice.</t>
         </is>
       </c>
     </row>
@@ -2421,7 +2433,7 @@
           <t>Wise Inc</t>
         </is>
       </c>
-      <c r="C27" s="16" t="n">
+      <c r="C27" s="14" t="n">
         <v>-334.17</v>
       </c>
       <c r="D27" s="10" t="inlineStr">
@@ -2429,19 +2441,19 @@
           <t>OUT</t>
         </is>
       </c>
-      <c r="E27" s="17" t="inlineStr">
-        <is>
-          <t>ASK</t>
-        </is>
-      </c>
-      <c r="F27" s="17" t="inlineStr">
-        <is>
-          <t>ASK</t>
+      <c r="E27" s="15" t="inlineStr">
+        <is>
+          <t>EPGC_EXPENSE</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>LOCKED</t>
         </is>
       </c>
       <c r="G27" s="10" t="inlineStr">
         <is>
-          <t>Wise — vendor / COGS / other</t>
+          <t>Wise — expertise write-ups (Consultant Fees)</t>
         </is>
       </c>
       <c r="H27" s="10" t="inlineStr">
@@ -2466,7 +2478,7 @@
       </c>
       <c r="L27" s="13" t="inlineStr">
         <is>
-          <t>International payment from EPGC. Not reimbursed. COGS, advisory cost, or personal?</t>
+          <t>User 2026-09-20: business expense (expertise write-ups). Hits EPGC Consultant Fees July $334.17. Not COGS, not reimbursed. Distinct from Dec Wise $565.75 (EOEB reimburse).</t>
         </is>
       </c>
     </row>
@@ -4041,7 +4053,7 @@
           <t>Wise Inc</t>
         </is>
       </c>
-      <c r="C54" s="16" t="n">
+      <c r="C54" s="14" t="n">
         <v>-658.63</v>
       </c>
       <c r="D54" s="10" t="inlineStr">
@@ -4049,19 +4061,19 @@
           <t>OUT</t>
         </is>
       </c>
-      <c r="E54" s="17" t="inlineStr">
-        <is>
-          <t>ASK</t>
-        </is>
-      </c>
-      <c r="F54" s="17" t="inlineStr">
-        <is>
-          <t>ASK</t>
+      <c r="E54" s="15" t="inlineStr">
+        <is>
+          <t>EPGC_EXPENSE</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>LOCKED</t>
         </is>
       </c>
       <c r="G54" s="10" t="inlineStr">
         <is>
-          <t>Wise — vendor / COGS / other</t>
+          <t>Wise — expertise write-ups (Consultant Fees)</t>
         </is>
       </c>
       <c r="H54" s="10" t="inlineStr">
@@ -4086,7 +4098,7 @@
       </c>
       <c r="L54" s="13" t="inlineStr">
         <is>
-          <t>International payment from EPGC. Not reimbursed. COGS, advisory cost, or personal?</t>
+          <t>User 2026-09-20: business expense (expertise write-ups). Hits EPGC Consultant Fees October $658.63. Not COGS, not reimbursed. Distinct from Dec Wise $565.75 (EOEB reimburse).</t>
         </is>
       </c>
     </row>
@@ -7225,20 +7237,42 @@
           <t>Consultant Fees</t>
         </is>
       </c>
-      <c r="B69" s="24" t="n"/>
-      <c r="C69" s="24" t="n"/>
-      <c r="D69" s="24" t="n"/>
-      <c r="E69" s="24" t="n"/>
-      <c r="F69" s="24" t="n"/>
-      <c r="G69" s="24" t="n"/>
-      <c r="H69" s="24" t="n"/>
-      <c r="I69" s="24" t="n"/>
-      <c r="J69" s="30" t="n">
+      <c r="B69" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="K69" s="24" t="n"/>
-      <c r="L69" s="24" t="n"/>
-      <c r="M69" s="24" t="n"/>
+      <c r="C69" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" s="28" t="n">
+        <v>334.17</v>
+      </c>
+      <c r="I69" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" s="28" t="n">
+        <v>658.63</v>
+      </c>
+      <c r="L69" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="N69" s="24">
         <f>SUM(B69:M69)</f>
         <v/>
@@ -7400,7 +7434,7 @@
     <row r="75">
       <c r="A75" s="13" t="inlineStr">
         <is>
-          <t>2025 Mercury 2026-09-20: Art Sales = MATCHED cash only (Berk $14,000 Jan + Berk $30,000 / mosaics $105,000 Feb = $149,000). Consultant June $13,595 = David Aaron Limited LOCKED (user: consultant fee, not a sale). EOEB remainder $130,270.00 and L5 $87,396.32 still ASK — not on Consultant. Koziol/Ariadne $150,000 LOCKED pass-through — not P&amp;L. Coinbase is Investments, not this tab. Newstar $23,581 is Art Sales COGS, not operating expense. 2024 leftover supplies/furniture/consultant-fee numbers on this 2025 block were zeroed. GCM 1099 is personal. Not tax advice.</t>
+          <t>2025 Mercury 2026-09-20: Art Sales = MATCHED cash only (Berk $14,000 Jan + Berk $30,000 / mosaics $105,000 Feb = $149,000). Consultant June $13,595 = David Aaron Limited LOCKED (user: consultant fee, not a sale). Consultant Fees July $334.17 + October $658.63 = Wise expertise write-ups LOCKED ($992.80). EOEB remainder $130,270.00 and L5 $87,396.32 still ASK — not on Consultant income. Koziol/Ariadne $150,000 LOCKED pass-through — not P&amp;L. Coinbase is Investments, not this tab. Newstar $23,581 is Art Sales COGS, not operating expense. Dec Wise $565.75 reimbursed — not on Consultant Fees. GCM 1099 is personal. Not tax advice.</t>
         </is>
       </c>
     </row>

--- a/.cursor/scratch/tax_turbo_parts/Personal Income 2025 — Mercury 8291.xlsx
+++ b/.cursor/scratch/tax_turbo_parts/Personal Income 2025 — Mercury 8291.xlsx
@@ -169,7 +169,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -293,6 +293,7 @@
     <xf numFmtId="164" fontId="12" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -667,7 +668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -678,7 +679,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ASK — remaining Mercury 8291 questions. Q6 consultant, Q7 Wise expertise write-ups, Q8 pass-through LOCKED 2026-09-20. Not tax advice.</t>
+          <t>ASK — remaining Mercury 8291 questions. Q6 consultant, Q7 Wise expertise write-ups, Q8 pass-through, Q9 Aquinas books LOCKED 2026-09-20. Not tax advice.</t>
         </is>
       </c>
     </row>
@@ -792,14 +793,14 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>9. Aquinas Hobor $1,000 IN (2/4)</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Sale, leftover, or other? Aquinas bought Saharan bracelets in 2022.</t>
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>9. Aquinas Hobor $1,000 IN (2/4) — LOCKED books sold</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>CONFIRMED 2026-09-20: books sold to Aquinas. Booked EPGC Art Sales February $1,000 (peach). Cost / titles TBD — not in Income I8 until Cost. Distinct from 2022 Saharan bracelets.</t>
         </is>
       </c>
     </row>
@@ -940,6 +941,18 @@
       <c r="B25" s="7" t="inlineStr">
         <is>
           <t>$334.17 (7/9) + $658.63 (10/30) = $992.80 → EPGC Consultant Fees expense. Dec $565.75 still reimbursed / not P&amp;L.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Aquinas Hobor books</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>$1,000 IN 2/4 LOCKED books sold → EPGC Art Sales February. Cost / titles TBD (not in I8 until Cost).</t>
         </is>
       </c>
     </row>
@@ -975,7 +988,7 @@
     <row r="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>Mercury Checking 8291 — EPGC LLC (Choice Financial) 2025. 64 unique cash transactions. Coinbase ACH = investment. Newstar = jewelry COGS on intaglios/gems/scarabs. BoA 9922 draws and Koziol/Ariadne $150k are LOCKED not-P&amp;L (pass-through / owner transfer). David Aaron $13,595 is LOCKED EPGC Consultant (June). Wise $334.17 + $658.63 are LOCKED EPGC Consultant Fees (expertise write-ups). Not tax advice.</t>
+          <t>Mercury Checking 8291 — EPGC LLC (Choice Financial) 2025. 64 unique cash transactions. Coinbase ACH = investment. Newstar = jewelry COGS on intaglios/gems/scarabs. BoA 9922 draws and Koziol/Ariadne $150k are LOCKED not-P&amp;L (pass-through / owner transfer). David Aaron $13,595 is LOCKED EPGC Consultant (June). Wise $334.17 + $658.63 are LOCKED EPGC Consultant Fees (expertise write-ups). Aquinas Hobor $1,000 (2/4) is LOCKED books sold (EPGC Art Sales February; Cost TBD). Not tax advice.</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1306,7 @@
           <t>AQUINAS HOBOR</t>
         </is>
       </c>
-      <c r="C8" s="16" t="n">
+      <c r="C8" s="14" t="n">
         <v>1000</v>
       </c>
       <c r="D8" s="10" t="inlineStr">
@@ -1301,31 +1314,31 @@
           <t>IN</t>
         </is>
       </c>
-      <c r="E8" s="17" t="inlineStr">
-        <is>
-          <t>ASK</t>
-        </is>
-      </c>
-      <c r="F8" s="17" t="inlineStr">
-        <is>
-          <t>ASK</t>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>ART_SALE</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>LOCKED</t>
         </is>
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t>Aquinas Hobor $1,000</t>
+          <t>Books sold to Aquinas Hobor — Sale Price</t>
         </is>
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I8" s="10" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
       <c r="J8" s="10" t="inlineStr">
         <is>
           <t>Transfer</t>
@@ -1338,7 +1351,7 @@
       </c>
       <c r="L8" s="13" t="inlineStr">
         <is>
-          <t>Prior-year buyer (Saharan bracelets 2022). 2025 sale, leftover, or something else?</t>
+          <t>User 2026-09-20: books sold to Aquinas. Hits EPGC Art Sales February $1,000. Cost / titles TBD (not in I8 net until Cost). Distinct from 2022 Saharan bracelets sale.</t>
         </is>
       </c>
     </row>
@@ -6618,7 +6631,7 @@
         <v>14000</v>
       </c>
       <c r="C53" s="28" t="n">
-        <v>135000</v>
+        <v>136000</v>
       </c>
       <c r="D53" s="11" t="n">
         <v>0</v>
@@ -7434,7 +7447,7 @@
     <row r="75">
       <c r="A75" s="13" t="inlineStr">
         <is>
-          <t>2025 Mercury 2026-09-20: Art Sales = MATCHED cash only (Berk $14,000 Jan + Berk $30,000 / mosaics $105,000 Feb = $149,000). Consultant June $13,595 = David Aaron Limited LOCKED (user: consultant fee, not a sale). Consultant Fees July $334.17 + October $658.63 = Wise expertise write-ups LOCKED ($992.80). EOEB remainder $130,270.00 and L5 $87,396.32 still ASK — not on Consultant income. Koziol/Ariadne $150,000 LOCKED pass-through — not P&amp;L. Coinbase is Investments, not this tab. Newstar $23,581 is Art Sales COGS, not operating expense. Dec Wise $565.75 reimbursed — not on Consultant Fees. GCM 1099 is personal. Not tax advice.</t>
+          <t>2025 Mercury 2026-09-20: Art Sales = MATCHED/LOCKED cash (Berk $14,000 Jan + Berk $30,000 / mosaics $105,000 / Aquinas books $1,000 Feb = $150,000). Consultant June $13,595 = David Aaron Limited LOCKED (user: consultant fee, not a sale). Consultant Fees July $334.17 + October $658.63 = Wise expertise write-ups LOCKED ($992.80). EOEB remainder $130,270.00 and L5 $87,396.32 still ASK — not on Consultant income. Koziol/Ariadne $150,000 LOCKED pass-through — not P&amp;L. Coinbase is Investments, not this tab. Newstar $23,581 is Art Sales COGS, not operating expense. Dec Wise $565.75 reimbursed — not on Consultant Fees. Aquinas books Cost TBD — cash on Art Sales, not in I8. GCM 1099 is personal. Not tax advice.</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N132"/>
+  <dimension ref="A1:N135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="47.86" customWidth="1" min="1" max="1"/>
@@ -10146,7 +10159,7 @@
     <row r="78">
       <c r="A78" s="56" t="inlineStr">
         <is>
-          <t>Mercury 8291 MATCHED: Berk $14,000 (1/10 seals) + $30,000 (2/7 lots). EOEB $105,000 (2/21 mosaics). Fortuna $13,000 (1/8 seals Cost). Plutus $50,000 of mosaics $90,000 Cost — $40,000 of Cost not on 8291 (ASK). Newstar $23,581 is jewelry fabrication COGS, parked below — not in sold-lot Cost (Berk gem/scarab lots already sold in February). David Aaron $13,595 (6/24) is LOCKED consultant fee — not a sale (EPGC Consultant June). Not tax advice.</t>
+          <t>Mercury 8291 MATCHED: Berk $14,000 (1/10 seals) + $30,000 (2/7 lots). EOEB $105,000 (2/21 mosaics). Fortuna $13,000 (1/8 seals Cost). Plutus $50,000 of mosaics $90,000 Cost — $40,000 of Cost not on 8291 (ASK). Newstar $23,581 is jewelry fabrication COGS, parked below — not in sold-lot Cost (Berk gem/scarab lots already sold in February). David Aaron $13,595 (6/24) is LOCKED consultant fee — not a sale (EPGC Consultant June). Aquinas Hobor $1,000 (2/4) is LOCKED books sold — EPGC Art Sales February; Cost TBD (not in I8). Not tax advice.</t>
         </is>
       </c>
     </row>
@@ -10997,6 +11010,48 @@
       </c>
       <c r="C132" s="58" t="n">
         <v>85000</v>
+      </c>
+    </row>
+    <row r="133"/>
+    <row r="134">
+      <c r="A134" s="59" t="inlineStr">
+        <is>
+          <t>2025 Mercury 8291 — Books sold to Aquinas Hobor (LOCKED)</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="7" t="inlineStr">
+        <is>
+          <t>Books sold to Aquinas Hobor (titles TBD)</t>
+        </is>
+      </c>
+      <c r="B135" s="7" t="inlineStr">
+        <is>
+          <t>Aquinas Hobor</t>
+        </is>
+      </c>
+      <c r="C135" s="7" t="n"/>
+      <c r="D135" s="7" t="n"/>
+      <c r="E135" s="7" t="inlineStr">
+        <is>
+          <t>Aquinas Hobor</t>
+        </is>
+      </c>
+      <c r="F135" s="14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G135" s="65" t="n">
+        <v>45692</v>
+      </c>
+      <c r="H135" s="7">
+        <f>IF(C135="","",F135-C135)</f>
+        <v/>
+      </c>
+      <c r="I135" s="7" t="inlineStr">
+        <is>
+          <t>LOCKED 2026-09-20: books sold to Aquinas. $1,000 cash on EPGC Art Sales February. Cost / titles TBD — not in Income I8 until Cost. Distinct from 2022 Saharan bracelets. Not tax advice.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -11068,7 +11123,7 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="65" t="inlineStr">
+      <c r="A5" s="66" t="inlineStr">
         <is>
           <t>Coinbase (ACH from Mercury 8291)</t>
         </is>
@@ -11177,19 +11232,19 @@
       <c r="I7" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="66" t="n">
+      <c r="J7" s="67" t="n">
         <v>-9000</v>
       </c>
-      <c r="K7" s="66" t="n">
+      <c r="K7" s="67" t="n">
         <v>-10000</v>
       </c>
-      <c r="L7" s="66" t="n">
+      <c r="L7" s="67" t="n">
         <v>-35000</v>
       </c>
-      <c r="M7" s="66" t="n">
+      <c r="M7" s="67" t="n">
         <v>-5000</v>
       </c>
-      <c r="N7" s="67">
+      <c r="N7" s="68">
         <f>SUM(B7:M7)</f>
         <v/>
       </c>
@@ -11233,10 +11288,10 @@
       <c r="L8" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="M8" s="66" t="n">
+      <c r="M8" s="67" t="n">
         <v>8000</v>
       </c>
-      <c r="N8" s="67">
+      <c r="N8" s="68">
         <f>SUM(B8:M8)</f>
         <v/>
       </c>
@@ -11283,14 +11338,14 @@
       <c r="M9" s="14" t="n">
         <v>3000</v>
       </c>
-      <c r="N9" s="67">
+      <c r="N9" s="68">
         <f>SUM(B9:M9)</f>
         <v/>
       </c>
     </row>
     <row r="10"/>
     <row r="11">
-      <c r="A11" s="68" t="inlineStr">
+      <c r="A11" s="69" t="inlineStr">
         <is>
           <t>2025: funded $59,000.00 / returned $8,000.00 / net $-51,000.00 off the EPGC operating account. Not income, not an expense. Not tax advice.</t>
         </is>
@@ -11418,11 +11473,11 @@
       <c r="E4" s="24" t="n">
         <v>115000</v>
       </c>
-      <c r="F4" s="69" t="n">
+      <c r="F4" s="70" t="n">
         <v>110000</v>
       </c>
-      <c r="G4" s="70" t="n"/>
-      <c r="H4" s="67" t="n">
+      <c r="G4" s="71" t="n"/>
+      <c r="H4" s="68" t="n">
         <v>110000</v>
       </c>
       <c r="I4" s="16" t="n">
@@ -11445,14 +11500,14 @@
         <v>1500</v>
       </c>
       <c r="E5" s="24" t="n"/>
-      <c r="F5" s="69" t="n">
+      <c r="F5" s="70" t="n">
         <v>1500</v>
       </c>
-      <c r="G5" s="70" t="n"/>
-      <c r="H5" s="67" t="n">
+      <c r="G5" s="71" t="n"/>
+      <c r="H5" s="68" t="n">
         <v>19500</v>
       </c>
-      <c r="I5" s="67" t="n">
+      <c r="I5" s="68" t="n">
         <v>19500</v>
       </c>
     </row>
@@ -11466,14 +11521,14 @@
       <c r="C6" s="24" t="n"/>
       <c r="D6" s="24" t="n"/>
       <c r="E6" s="24" t="n"/>
-      <c r="F6" s="69" t="n">
+      <c r="F6" s="70" t="n">
         <v>20000</v>
       </c>
-      <c r="G6" s="70" t="n"/>
-      <c r="H6" s="67" t="n">
+      <c r="G6" s="71" t="n"/>
+      <c r="H6" s="68" t="n">
         <v>17000</v>
       </c>
-      <c r="I6" s="67" t="n">
+      <c r="I6" s="68" t="n">
         <v>17086.94</v>
       </c>
     </row>
@@ -11495,14 +11550,14 @@
       <c r="E7" s="24" t="n">
         <v>14700</v>
       </c>
-      <c r="F7" s="69" t="n">
+      <c r="F7" s="70" t="n">
         <v>16000</v>
       </c>
-      <c r="G7" s="69" t="n"/>
-      <c r="H7" s="67" t="n">
+      <c r="G7" s="70" t="n"/>
+      <c r="H7" s="68" t="n">
         <v>21500</v>
       </c>
-      <c r="I7" s="67" t="n">
+      <c r="I7" s="68" t="n">
         <v>21500</v>
       </c>
     </row>
@@ -11524,11 +11579,11 @@
       <c r="E8" s="24" t="n">
         <v>54777.25</v>
       </c>
-      <c r="F8" s="69" t="n">
+      <c r="F8" s="70" t="n">
         <v>20000</v>
       </c>
-      <c r="G8" s="70" t="n"/>
-      <c r="H8" s="67" t="n">
+      <c r="G8" s="71" t="n"/>
+      <c r="H8" s="68" t="n">
         <v>20000</v>
       </c>
       <c r="I8" s="16" t="n">
@@ -11551,14 +11606,14 @@
         <v>74000</v>
       </c>
       <c r="E9" s="24" t="n"/>
-      <c r="F9" s="69" t="n">
+      <c r="F9" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="70" t="n"/>
-      <c r="H9" s="67" t="n">
+      <c r="G9" s="71" t="n"/>
+      <c r="H9" s="68" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="67" t="n">
+      <c r="I9" s="68" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11584,19 +11639,19 @@
         <f>SUM(E4:E9)</f>
         <v/>
       </c>
-      <c r="F10" s="69">
+      <c r="F10" s="70">
         <f>SUM(F4:F9)</f>
         <v/>
       </c>
-      <c r="G10" s="69">
+      <c r="G10" s="70">
         <f>SUM(G4:G9)</f>
         <v/>
       </c>
-      <c r="H10" s="69">
+      <c r="H10" s="70">
         <f>SUM(H4:H9)</f>
         <v/>
       </c>
-      <c r="I10" s="69">
+      <c r="I10" s="70">
         <f>SUM(I4:I9)</f>
         <v/>
       </c>
@@ -11606,9 +11661,9 @@
       <c r="B11" s="24" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="68" t="inlineStr">
-        <is>
-          <t>2025 Actual: I4 Monarch paycheck cash ≠ W-2 Box 1. I5 216 LTR cash $19,500. I6 524 #2 STR platform net LOCKED. I7 GCM 1099-NEC $21,500. I8 Art net $23,055.06 = MATCHED Mercury deals only (Berk lots $30,000 − $22,944.94 Cost) + seals $1,000 + mosaics $15,000. Excludes Sale 6428 $11,000 until Cost. David Aaron $13,595 is EPGC Consultant June (not I8). Erdal/Aysel/EOEB/L5 ASK. Not tax advice.</t>
+      <c r="A12" s="69" t="inlineStr">
+        <is>
+          <t>2025 Actual: I4 Monarch paycheck cash ≠ W-2 Box 1. I5 216 LTR cash $19,500. I6 524 #2 STR platform net LOCKED. I7 GCM 1099-NEC $21,500. I8 Art net $23,055.06 = MATCHED Mercury deals only (Berk lots $30,000 − $22,944.94 Cost) + seals $1,000 + mosaics $15,000. Excludes Sale 6428 $11,000 until Cost. Excludes Aquinas books $1,000 until Cost. David Aaron $13,595 is EPGC Consultant June (not I8). Erdal/Aysel/EOEB/L5 ASK. Not tax advice.</t>
         </is>
       </c>
       <c r="B12" s="24" t="n"/>

--- a/.cursor/scratch/tax_turbo_parts/Personal Income 2025 — Mercury 8291.xlsx
+++ b/.cursor/scratch/tax_turbo_parts/Personal Income 2025 — Mercury 8291.xlsx
@@ -169,7 +169,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -280,6 +280,11 @@
     <xf numFmtId="164" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -292,8 +297,6 @@
     <xf numFmtId="0" fontId="12" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="12" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -679,7 +682,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ASK — remaining Mercury 8291 questions. Q6 consultant, Q7 Wise expertise write-ups, Q8 pass-through, Q9 Aquinas books LOCKED 2026-09-20. Not tax advice.</t>
+          <t>ASK — remaining Mercury 8291 questions. Q6 consultant, Q7 Wise expertise, Q8 pass-through, Q9 Aquinas books LOCKED (green). Q1/Q2 mixed pattern CONFIRMED, dollars unallocated (yellow). Not tax advice.</t>
         </is>
       </c>
     </row>
@@ -699,24 +702,24 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>1. EOEB LLC remainder after mosaics</t>
+          <t>1. EOEB LLC remainder after mosaics — MIXED PATTERN CONFIRMED, dollars unallocated</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>$130,270.00 of EOEB IN is not the $105,000 mosaics sale and not the $565.75 Wise reimbursement. Invoice / MAKE A PAYMENT pattern. Book as art advisory (EPGC Consultant) or as more art sales? Jan 16 $1,000 might be the Canosan horse (sold to Erdal $1,000 on Art Sales) — yes/no?</t>
+          <t>$130,270.00 of EOEB IN is not mosaics $105,000 and not Wise reimburse $565.75. User 2026-09-20: EOEB is mixed art sales AND advisory/consultant fees. Do NOT dump this remainder onto Consultant or Art Sales. Invoice-level split still ASK. Jan 16 $1,000 Canosan-horse question STILL OPEN (Art Sales horse is to Erdal; this cash is EOEB).</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2. L5 (all seven invoices)</t>
+          <t>2. L5 (all seven invoices) — MIXED PATTERN CONFIRMED, dollars unallocated</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>$87,396.32. Same Auto-Routing Request or Invoice Payment pattern as EOEB. Advisory fees, art sales, or mixed? The 7/15 $50,000 lands the same week as Aysel $50k and Fortuna $45k.</t>
+          <t>$87,396.32. User 2026-09-20: L5 is mixed art sales AND advisory/consultant fees. Do NOT dump onto Consultant or Art Sales. Invoice-level split still ASK. The 7/15 $50,000 still sits in the Aysel $50k / Fortuna $45k week.</t>
         </is>
       </c>
     </row>
@@ -795,12 +798,12 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>9. Aquinas Hobor $1,000 IN (2/4) — LOCKED books sold</t>
+          <t>9. Aquinas Hobor $1,000 IN (2/4) — LOCKED book sale</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>CONFIRMED 2026-09-20: books sold to Aquinas. Booked EPGC Art Sales February $1,000 (peach). Cost / titles TBD — not in Income I8 until Cost. Distinct from 2022 Saharan bracelets.</t>
+          <t>CONFIRMED 2026-09-20: book SALE. Hits EPGC Art Sales February +$1,000 (Feb $136,000; matched cash $150,000). Art Sales register: Books (titles TBD) to Aquinas Hobor, Sale Price $1,000, Sale Date 2025-02-04, Cost TBD. Not in Income I8 until Cost (same as Sale 6428).</t>
         </is>
       </c>
     </row>
@@ -952,7 +955,7 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>$1,000 IN 2/4 LOCKED books sold → EPGC Art Sales February. Cost / titles TBD (not in I8 until Cost).</t>
+          <t>$1,000 IN 2/4 LOCKED book sale → EPGC Art Sales February +$1,000 (Feb $136,000; matched cash $150,000). Cost / titles TBD (not in I8 until Cost, same as Sale 6428).</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1209,7 @@
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>EOEB $1,000 — Canosan horse vs advisory</t>
+          <t>EOEB $1,000 — Canosan horse vs advisory (STILL OPEN)</t>
         </is>
       </c>
       <c r="H6" s="10" t="inlineStr">
@@ -1231,7 +1234,7 @@
       </c>
       <c r="L6" s="13" t="inlineStr">
         <is>
-          <t>Art Sales has Canosan Terracotta Horse to Erdal $1,000. This cash is EOEB, not Erdal. Sale or advisory invoice?</t>
+          <t>STILL OPEN after mixed-pattern confirm. Art Sales has Canosan Terracotta Horse to Erdal $1,000. This cash is EOEB, not Erdal. Sale of the horse, advisory invoice, or other? Not allocated.</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1329,7 @@
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t>Books sold to Aquinas Hobor — Sale Price</t>
+          <t>Books (titles TBD) — Sale Price</t>
         </is>
       </c>
       <c r="H8" s="10" t="inlineStr">
@@ -1351,7 +1354,7 @@
       </c>
       <c r="L8" s="13" t="inlineStr">
         <is>
-          <t>User 2026-09-20: books sold to Aquinas. Hits EPGC Art Sales February $1,000. Cost / titles TBD (not in I8 net until Cost). Distinct from 2022 Saharan bracelets sale.</t>
+          <t>User 2026-09-20: book SALE to Aquinas Hobor. Hits EPGC Art Sales February +$1,000. Art Sales register: Books (titles TBD), Cost TBD. Not in Income I8 until Cost is known (same as Sale 6428).</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1929,7 @@
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>EOEB — sale vs art advisory</t>
+          <t>EOEB — mixed unallocated (sale vs advisory)</t>
         </is>
       </c>
       <c r="H18" s="10" t="inlineStr">
@@ -1951,7 +1954,7 @@
       </c>
       <c r="L18" s="13" t="inlineStr">
         <is>
-          <t>Invoice / MAKE A PAYMENT. Not matched to an Art Sales object. Proposed advisory (Consultant) until you say otherwise.</t>
+          <t>User 2026-09-20: EOEB LLC mixed art sales AND advisory/consultant fees. Pattern confirmed; this invoice still unallocated. Do NOT dump EOEB remainder $130,270 onto Consultant or Art Sales. Invoice-level split still ASK.</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1989,7 @@
       </c>
       <c r="G19" s="10" t="inlineStr">
         <is>
-          <t>EOEB — sale vs art advisory</t>
+          <t>EOEB — mixed unallocated (sale vs advisory)</t>
         </is>
       </c>
       <c r="H19" s="10" t="inlineStr">
@@ -2011,7 +2014,7 @@
       </c>
       <c r="L19" s="13" t="inlineStr">
         <is>
-          <t>Invoice / MAKE A PAYMENT. Proposed advisory until confirmed.</t>
+          <t>User 2026-09-20: EOEB LLC mixed art sales AND advisory/consultant fees. Pattern confirmed; this invoice still unallocated. Do NOT dump EOEB remainder $130,270 onto Consultant or Art Sales. Invoice-level split still ASK.</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2109,7 @@
       </c>
       <c r="G21" s="10" t="inlineStr">
         <is>
-          <t>EOEB — sale vs art advisory</t>
+          <t>EOEB — mixed unallocated (sale vs advisory)</t>
         </is>
       </c>
       <c r="H21" s="10" t="inlineStr">
@@ -2131,7 +2134,7 @@
       </c>
       <c r="L21" s="13" t="inlineStr">
         <is>
-          <t>Invoice / MAKE A PAYMENT. Proposed advisory until confirmed.</t>
+          <t>User 2026-09-20: EOEB LLC mixed art sales AND advisory/consultant fees. Pattern confirmed; this invoice still unallocated. Do NOT dump EOEB remainder $130,270 onto Consultant or Art Sales. Invoice-level split still ASK.</t>
         </is>
       </c>
     </row>
@@ -2166,7 +2169,7 @@
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>EOEB — sale vs art advisory</t>
+          <t>EOEB — mixed unallocated (sale vs advisory)</t>
         </is>
       </c>
       <c r="H22" s="10" t="inlineStr">
@@ -2191,7 +2194,7 @@
       </c>
       <c r="L22" s="13" t="inlineStr">
         <is>
-          <t>Invoice / MAKE A PAYMENT. Proposed advisory until confirmed.</t>
+          <t>User 2026-09-20: EOEB LLC mixed art sales AND advisory/consultant fees. Pattern confirmed; this invoice still unallocated. Do NOT dump EOEB remainder $130,270 onto Consultant or Art Sales. Invoice-level split still ASK.</t>
         </is>
       </c>
     </row>
@@ -2226,7 +2229,7 @@
       </c>
       <c r="G23" s="10" t="inlineStr">
         <is>
-          <t>EOEB — sale vs art advisory</t>
+          <t>EOEB — mixed unallocated (sale vs advisory)</t>
         </is>
       </c>
       <c r="H23" s="10" t="inlineStr">
@@ -2251,7 +2254,7 @@
       </c>
       <c r="L23" s="13" t="inlineStr">
         <is>
-          <t>Invoice / MAKE A PAYMENT. Proposed advisory until confirmed.</t>
+          <t>User 2026-09-20: EOEB LLC mixed art sales AND advisory/consultant fees. Pattern confirmed; this invoice still unallocated. Do NOT dump EOEB remainder $130,270 onto Consultant or Art Sales. Invoice-level split still ASK.</t>
         </is>
       </c>
     </row>
@@ -2406,7 +2409,7 @@
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>EOEB — sale vs art advisory</t>
+          <t>EOEB — mixed unallocated (sale vs advisory)</t>
         </is>
       </c>
       <c r="H26" s="10" t="inlineStr">
@@ -2431,7 +2434,7 @@
       </c>
       <c r="L26" s="13" t="inlineStr">
         <is>
-          <t>Auto-Routing Request or Invoice Payment. Proposed advisory until confirmed.</t>
+          <t>User 2026-09-20: EOEB LLC mixed art sales AND advisory/consultant fees. Pattern confirmed; this invoice still unallocated. Do NOT dump EOEB remainder $130,270 onto Consultant or Art Sales. Invoice-level split still ASK.</t>
         </is>
       </c>
     </row>
@@ -2526,7 +2529,7 @@
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>L5 — sale vs art advisory</t>
+          <t>L5 — mixed unallocated (sale vs advisory)</t>
         </is>
       </c>
       <c r="H28" s="10" t="inlineStr">
@@ -2551,7 +2554,7 @@
       </c>
       <c r="L28" s="13" t="inlineStr">
         <is>
-          <t>Auto-Routing Request or Invoice Payment. Same invoice pattern as EOEB. Proposed advisory until confirmed.</t>
+          <t>User 2026-09-20: L5 LLC mixed art sales AND advisory/consultant fees. Pattern confirmed; this invoice still unallocated. Do NOT dump L5 remainder $87,396.32 onto Consultant or Art Sales. Invoice-level split still ASK.</t>
         </is>
       </c>
     </row>
@@ -2586,7 +2589,7 @@
       </c>
       <c r="G29" s="10" t="inlineStr">
         <is>
-          <t>L5 — sale vs art advisory</t>
+          <t>L5 — mixed unallocated (sale vs advisory)</t>
         </is>
       </c>
       <c r="H29" s="10" t="inlineStr">
@@ -2611,7 +2614,7 @@
       </c>
       <c r="L29" s="13" t="inlineStr">
         <is>
-          <t>Auto-Routing Request or Invoice Payment. Proposed advisory until confirmed.</t>
+          <t>User 2026-09-20: L5 LLC mixed art sales AND advisory/consultant fees. Pattern confirmed; this invoice still unallocated. Do NOT dump L5 remainder $87,396.32 onto Consultant or Art Sales. Invoice-level split still ASK.</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2649,7 @@
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>L5 $50,000 — sale vs art advisory vs pass-through</t>
+          <t>L5 $50,000 — mixed unallocated (sale vs advisory)</t>
         </is>
       </c>
       <c r="H30" s="10" t="inlineStr">
@@ -2671,7 +2674,7 @@
       </c>
       <c r="L30" s="13" t="inlineStr">
         <is>
-          <t>Largest L5 invoice. Sale of an object, advisory, or pass-through? Same week as Aysel $50k IN and Fortuna $45k OUT.</t>
+          <t>User 2026-09-20: L5 LLC mixed art sales AND advisory/consultant fees. Pattern confirmed; this invoice still unallocated. Do NOT dump L5 remainder $87,396.32 onto Consultant or Art Sales. Invoice-level split still ASK. Same week as Aysel $50k IN and Fortuna $45k OUT.</t>
         </is>
       </c>
     </row>
@@ -3006,7 +3009,7 @@
       </c>
       <c r="G36" s="10" t="inlineStr">
         <is>
-          <t>EOEB — sale vs art advisory</t>
+          <t>EOEB — mixed unallocated (sale vs advisory)</t>
         </is>
       </c>
       <c r="H36" s="10" t="inlineStr">
@@ -3031,7 +3034,7 @@
       </c>
       <c r="L36" s="13" t="inlineStr">
         <is>
-          <t>Auto-Routing. Proposed advisory until confirmed.</t>
+          <t>User 2026-09-20: EOEB LLC mixed art sales AND advisory/consultant fees. Pattern confirmed; this invoice still unallocated. Do NOT dump EOEB remainder $130,270 onto Consultant or Art Sales. Invoice-level split still ASK.</t>
         </is>
       </c>
     </row>
@@ -3066,7 +3069,7 @@
       </c>
       <c r="G37" s="10" t="inlineStr">
         <is>
-          <t>L5 — sale vs art advisory</t>
+          <t>L5 — mixed unallocated (sale vs advisory)</t>
         </is>
       </c>
       <c r="H37" s="10" t="inlineStr">
@@ -3091,7 +3094,7 @@
       </c>
       <c r="L37" s="13" t="inlineStr">
         <is>
-          <t>Auto-Routing. Proposed advisory until confirmed.</t>
+          <t>User 2026-09-20: L5 LLC mixed art sales AND advisory/consultant fees. Pattern confirmed; this invoice still unallocated. Do NOT dump L5 remainder $87,396.32 onto Consultant or Art Sales. Invoice-level split still ASK.</t>
         </is>
       </c>
     </row>
@@ -3186,7 +3189,7 @@
       </c>
       <c r="G39" s="10" t="inlineStr">
         <is>
-          <t>EOEB — sale vs art advisory</t>
+          <t>EOEB — mixed unallocated (sale vs advisory)</t>
         </is>
       </c>
       <c r="H39" s="10" t="inlineStr">
@@ -3211,7 +3214,7 @@
       </c>
       <c r="L39" s="13" t="inlineStr">
         <is>
-          <t>Auto-Routing. Proposed advisory until confirmed.</t>
+          <t>User 2026-09-20: EOEB LLC mixed art sales AND advisory/consultant fees. Pattern confirmed; this invoice still unallocated. Do NOT dump EOEB remainder $130,270 onto Consultant or Art Sales. Invoice-level split still ASK.</t>
         </is>
       </c>
     </row>
@@ -3246,7 +3249,7 @@
       </c>
       <c r="G40" s="10" t="inlineStr">
         <is>
-          <t>L5 — sale vs art advisory</t>
+          <t>L5 — mixed unallocated (sale vs advisory)</t>
         </is>
       </c>
       <c r="H40" s="10" t="inlineStr">
@@ -3271,7 +3274,7 @@
       </c>
       <c r="L40" s="13" t="inlineStr">
         <is>
-          <t>Auto-Routing. Proposed advisory until confirmed.</t>
+          <t>User 2026-09-20: L5 LLC mixed art sales AND advisory/consultant fees. Pattern confirmed; this invoice still unallocated. Do NOT dump L5 remainder $87,396.32 onto Consultant or Art Sales. Invoice-level split still ASK.</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3369,7 @@
       </c>
       <c r="G42" s="10" t="inlineStr">
         <is>
-          <t>EOEB — sale vs art advisory</t>
+          <t>EOEB — mixed unallocated (sale vs advisory)</t>
         </is>
       </c>
       <c r="H42" s="10" t="inlineStr">
@@ -3391,7 +3394,7 @@
       </c>
       <c r="L42" s="13" t="inlineStr">
         <is>
-          <t>Auto-Routing. Proposed advisory until confirmed.</t>
+          <t>User 2026-09-20: EOEB LLC mixed art sales AND advisory/consultant fees. Pattern confirmed; this invoice still unallocated. Do NOT dump EOEB remainder $130,270 onto Consultant or Art Sales. Invoice-level split still ASK.</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3549,7 @@
       </c>
       <c r="G45" s="10" t="inlineStr">
         <is>
-          <t>EOEB — sale vs art advisory</t>
+          <t>EOEB — mixed unallocated (sale vs advisory)</t>
         </is>
       </c>
       <c r="H45" s="10" t="inlineStr">
@@ -3571,7 +3574,7 @@
       </c>
       <c r="L45" s="13" t="inlineStr">
         <is>
-          <t>Auto-Routing. Proposed advisory until confirmed.</t>
+          <t>User 2026-09-20: EOEB LLC mixed art sales AND advisory/consultant fees. Pattern confirmed; this invoice still unallocated. Do NOT dump EOEB remainder $130,270 onto Consultant or Art Sales. Invoice-level split still ASK.</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3789,7 @@
       </c>
       <c r="G49" s="10" t="inlineStr">
         <is>
-          <t>EOEB — sale vs art advisory</t>
+          <t>EOEB — mixed unallocated (sale vs advisory)</t>
         </is>
       </c>
       <c r="H49" s="10" t="inlineStr">
@@ -3811,7 +3814,7 @@
       </c>
       <c r="L49" s="13" t="inlineStr">
         <is>
-          <t>Auto-Routing. Proposed advisory until confirmed.</t>
+          <t>User 2026-09-20: EOEB LLC mixed art sales AND advisory/consultant fees. Pattern confirmed; this invoice still unallocated. Do NOT dump EOEB remainder $130,270 onto Consultant or Art Sales. Invoice-level split still ASK.</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3969,7 @@
       </c>
       <c r="G52" s="10" t="inlineStr">
         <is>
-          <t>L5 — sale vs art advisory</t>
+          <t>L5 — mixed unallocated (sale vs advisory)</t>
         </is>
       </c>
       <c r="H52" s="10" t="inlineStr">
@@ -3991,7 +3994,7 @@
       </c>
       <c r="L52" s="13" t="inlineStr">
         <is>
-          <t>Auto-Routing. Proposed advisory until confirmed.</t>
+          <t>User 2026-09-20: L5 LLC mixed art sales AND advisory/consultant fees. Pattern confirmed; this invoice still unallocated. Do NOT dump L5 remainder $87,396.32 onto Consultant or Art Sales. Invoice-level split still ASK.</t>
         </is>
       </c>
     </row>
@@ -4026,7 +4029,7 @@
       </c>
       <c r="G53" s="10" t="inlineStr">
         <is>
-          <t>EOEB — sale vs art advisory</t>
+          <t>EOEB — mixed unallocated (sale vs advisory)</t>
         </is>
       </c>
       <c r="H53" s="10" t="inlineStr">
@@ -4051,7 +4054,7 @@
       </c>
       <c r="L53" s="13" t="inlineStr">
         <is>
-          <t>Auto-Routing. Proposed advisory until confirmed.</t>
+          <t>User 2026-09-20: EOEB LLC mixed art sales AND advisory/consultant fees. Pattern confirmed; this invoice still unallocated. Do NOT dump EOEB remainder $130,270 onto Consultant or Art Sales. Invoice-level split still ASK.</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4149,7 @@
       </c>
       <c r="G55" s="10" t="inlineStr">
         <is>
-          <t>EOEB — sale vs art advisory</t>
+          <t>EOEB — mixed unallocated (sale vs advisory)</t>
         </is>
       </c>
       <c r="H55" s="10" t="inlineStr">
@@ -4171,7 +4174,7 @@
       </c>
       <c r="L55" s="13" t="inlineStr">
         <is>
-          <t>Auto-Routing. Proposed advisory until confirmed.</t>
+          <t>User 2026-09-20: EOEB LLC mixed art sales AND advisory/consultant fees. Pattern confirmed; this invoice still unallocated. Do NOT dump EOEB remainder $130,270 onto Consultant or Art Sales. Invoice-level split still ASK.</t>
         </is>
       </c>
     </row>
@@ -4686,7 +4689,7 @@
       </c>
       <c r="G64" s="10" t="inlineStr">
         <is>
-          <t>L5 — sale vs art advisory</t>
+          <t>L5 — mixed unallocated (sale vs advisory)</t>
         </is>
       </c>
       <c r="H64" s="10" t="inlineStr">
@@ -4711,7 +4714,7 @@
       </c>
       <c r="L64" s="13" t="inlineStr">
         <is>
-          <t>Auto-Routing. Proposed advisory until confirmed.</t>
+          <t>User 2026-09-20: L5 LLC mixed art sales AND advisory/consultant fees. Pattern confirmed; this invoice still unallocated. Do NOT dump L5 remainder $87,396.32 onto Consultant or Art Sales. Invoice-level split still ASK.</t>
         </is>
       </c>
     </row>
@@ -7447,7 +7450,7 @@
     <row r="75">
       <c r="A75" s="13" t="inlineStr">
         <is>
-          <t>2025 Mercury 2026-09-20: Art Sales = MATCHED/LOCKED cash (Berk $14,000 Jan + Berk $30,000 / mosaics $105,000 / Aquinas books $1,000 Feb = $150,000). Consultant June $13,595 = David Aaron Limited LOCKED (user: consultant fee, not a sale). Consultant Fees July $334.17 + October $658.63 = Wise expertise write-ups LOCKED ($992.80). EOEB remainder $130,270.00 and L5 $87,396.32 still ASK — not on Consultant income. Koziol/Ariadne $150,000 LOCKED pass-through — not P&amp;L. Coinbase is Investments, not this tab. Newstar $23,581 is Art Sales COGS, not operating expense. Dec Wise $565.75 reimbursed — not on Consultant Fees. Aquinas books Cost TBD — cash on Art Sales, not in I8. GCM 1099 is personal. Not tax advice.</t>
+          <t>2025 Mercury 2026-09-20: Art Sales = MATCHED/LOCKED cash (Berk $14,000 Jan + Berk $30,000 / mosaics $105,000 / Aquinas books $1,000 Feb = $150,000). Consultant June $13,595 = David Aaron Limited LOCKED (user: consultant fee, not a sale). Consultant Fees July $334.17 + October $658.63 = Wise expertise write-ups LOCKED ($992.80). EOEB remainder $130,270.00 and L5 $87,396.32 MIXED PATTERN CONFIRMED (art sales + advisory/consultant) — invoice-level split still ASK; not dumped onto Consultant or Art Sales. Koziol/Ariadne $150,000 LOCKED pass-through — not P&amp;L. Coinbase is Investments, not this tab. Newstar $23,581 is Art Sales COGS, not operating expense. Dec Wise $565.75 reimbursed — not on Consultant Fees. Aquinas books Cost TBD — cash on Art Sales, not in I8. GCM 1099 is personal. Not tax advice.</t>
         </is>
       </c>
     </row>
@@ -7464,7 +7467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N135"/>
+  <dimension ref="A1:N134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="47.86" customWidth="1" min="1" max="1"/>
@@ -10139,82 +10142,85 @@
       <c r="I76" s="33" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="35" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B77" s="32" t="n"/>
-      <c r="C77" s="46" t="n"/>
-      <c r="D77" s="45" t="n"/>
-      <c r="E77" s="45" t="n"/>
-      <c r="F77" s="46" t="n"/>
-      <c r="G77" s="45" t="n"/>
-      <c r="H77" s="46">
-        <f>SUM(H51:H75)</f>
-        <v/>
-      </c>
-      <c r="I77" s="33" t="n"/>
+      <c r="A77" s="7" t="inlineStr">
+        <is>
+          <t>Books (titles TBD)</t>
+        </is>
+      </c>
+      <c r="B77" s="17" t="inlineStr">
+        <is>
+          <t>Cost TBD</t>
+        </is>
+      </c>
+      <c r="C77" s="56" t="n"/>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>Aquinas Hobor</t>
+        </is>
+      </c>
+      <c r="F77" s="14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G77" s="57" t="n">
+        <v>45692</v>
+      </c>
+      <c r="H77" s="10">
+        <f>IF(OR(F77="",C77=""),"",F77-C77)</f>
+        <v/>
+      </c>
+      <c r="I77" s="4" t="inlineStr">
+        <is>
+          <t>LOCKED 2026-09-20: book SALE $1,000 on Mercury 8291. Cost TBD — not in Income I8 yet (same as Sale 6428). Titles TBD. Not tax advice.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
-      <c r="A78" s="56" t="inlineStr">
+      <c r="A78" s="58" t="inlineStr">
         <is>
           <t>Mercury 8291 MATCHED: Berk $14,000 (1/10 seals) + $30,000 (2/7 lots). EOEB $105,000 (2/21 mosaics). Fortuna $13,000 (1/8 seals Cost). Plutus $50,000 of mosaics $90,000 Cost — $40,000 of Cost not on 8291 (ASK). Newstar $23,581 is jewelry fabrication COGS, parked below — not in sold-lot Cost (Berk gem/scarab lots already sold in February). David Aaron $13,595 (6/24) is LOCKED consultant fee — not a sale (EPGC Consultant June). Aquinas Hobor $1,000 (2/4) is LOCKED books sold — EPGC Art Sales February; Cost TBD (not in I8). Not tax advice.</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="21" t="inlineStr">
+      <c r="A79" s="59" t="inlineStr">
+        <is>
+          <t>Mercury 8291 MATCHED: Berk $14,000 (1/10 seals) + $30,000 (2/7 lots). EOEB $105,000 (2/21 mosaics). Fortuna $13,000 (1/8 seals Cost). Plutus $50,000 of mosaics $90,000 Cost — $40,000 of Cost not on 8291 (ASK). Newstar $23,581 is jewelry fabrication COGS, parked below — not in sold-lot Cost (Berk gem/scarab lots already sold in February). David Aaron $13,595 (6/24) is LOCKED consultant fee — not a sale (EPGC Consultant June). Aquinas Hobor $1,000 (2/4) is LOCKED books sold — EPGC Art Sales February; Cost TBD (not in I8). Not tax advice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="21" t="inlineStr">
         <is>
           <t>Art Purchases/Inventory</t>
         </is>
       </c>
-      <c r="B79" s="32" t="n"/>
-      <c r="C79" s="24" t="n"/>
-      <c r="D79" s="39" t="n"/>
-      <c r="E79" s="57" t="n"/>
-      <c r="F79" s="24" t="n"/>
-      <c r="G79" s="39" t="n"/>
-      <c r="H79" s="57" t="n"/>
-      <c r="I79" s="33" t="n"/>
-      <c r="J79" s="57" t="n"/>
-      <c r="K79" s="57" t="n"/>
-      <c r="L79" s="57" t="n"/>
-      <c r="M79" s="57" t="n"/>
-      <c r="N79" s="57" t="n"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="23" t="inlineStr">
-        <is>
-          <t>30 Paleothic and Neolithic Stone Tools</t>
-        </is>
-      </c>
-      <c r="B80" s="48" t="inlineStr">
-        <is>
-          <t>Holestein</t>
-        </is>
-      </c>
-      <c r="C80" s="24" t="n">
-        <v>4000</v>
-      </c>
-      <c r="E80" s="33" t="n"/>
+      <c r="B80" s="32" t="n"/>
+      <c r="C80" s="24" t="n"/>
+      <c r="D80" s="39" t="n"/>
+      <c r="E80" s="60" t="n"/>
+      <c r="F80" s="24" t="n"/>
+      <c r="G80" s="39" t="n"/>
+      <c r="H80" s="60" t="n"/>
+      <c r="I80" s="33" t="n"/>
+      <c r="J80" s="60" t="n"/>
+      <c r="K80" s="60" t="n"/>
+      <c r="L80" s="60" t="n"/>
+      <c r="M80" s="60" t="n"/>
+      <c r="N80" s="60" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="23" t="inlineStr">
         <is>
-          <t>A Tairona Figure</t>
+          <t>30 Paleothic and Neolithic Stone Tools</t>
         </is>
       </c>
       <c r="B81" s="48" t="inlineStr">
         <is>
-          <t>Live Auctioneers</t>
+          <t>Holestein</t>
         </is>
       </c>
       <c r="C81" s="24" t="n">
-        <v>250</v>
-      </c>
-      <c r="D81" s="39" t="n">
-        <v>45119</v>
+        <v>4000</v>
       </c>
       <c r="E81" s="33" t="n"/>
     </row>
@@ -10230,7 +10236,7 @@
         </is>
       </c>
       <c r="C82" s="24" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="D82" s="39" t="n">
         <v>45119</v>
@@ -10240,26 +10246,26 @@
     <row r="83">
       <c r="A83" s="23" t="inlineStr">
         <is>
-          <t>A Pair of Greek Bronze Greeves</t>
+          <t>A Tairona Figure</t>
         </is>
       </c>
       <c r="B83" s="48" t="inlineStr">
         <is>
-          <t>ebay</t>
+          <t>Live Auctioneers</t>
         </is>
       </c>
       <c r="C83" s="24" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="D83" s="39" t="n">
-        <v>45145</v>
+        <v>45119</v>
       </c>
       <c r="E83" s="33" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="23" t="inlineStr">
         <is>
-          <t>An Illyrian Bronze Helmet</t>
+          <t>A Pair of Greek Bronze Greeves</t>
         </is>
       </c>
       <c r="B84" s="48" t="inlineStr">
@@ -10268,58 +10274,57 @@
         </is>
       </c>
       <c r="C84" s="24" t="n">
-        <v>551.25</v>
+        <v>200</v>
       </c>
       <c r="D84" s="39" t="n">
-        <v>45114</v>
+        <v>45145</v>
       </c>
       <c r="E84" s="33" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="23" t="inlineStr">
         <is>
-          <t>An Egyptian Faience Ibis</t>
-        </is>
-      </c>
-      <c r="B85" s="32" t="inlineStr">
-        <is>
-          <t>Hindman</t>
+          <t>An Illyrian Bronze Helmet</t>
+        </is>
+      </c>
+      <c r="B85" s="48" t="inlineStr">
+        <is>
+          <t>ebay</t>
         </is>
       </c>
       <c r="C85" s="24" t="n">
-        <v>375</v>
+        <v>551.25</v>
       </c>
       <c r="D85" s="39" t="n">
-        <v>44343</v>
-      </c>
-      <c r="E85" s="39" t="n"/>
-      <c r="F85" s="24" t="n"/>
-      <c r="I85" s="33" t="n"/>
+        <v>45114</v>
+      </c>
+      <c r="E85" s="33" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="23" t="inlineStr">
         <is>
-          <t>African Stone Bracelet Upper Volta River 1 0f 4</t>
+          <t>An Egyptian Faience Ibis</t>
         </is>
       </c>
       <c r="B86" s="32" t="inlineStr">
         <is>
-          <t>Live Auctioneers</t>
+          <t>Hindman</t>
         </is>
       </c>
       <c r="C86" s="24" t="n">
-        <v>293</v>
+        <v>375</v>
       </c>
       <c r="D86" s="39" t="n">
-        <v>44548</v>
-      </c>
+        <v>44343</v>
+      </c>
+      <c r="E86" s="39" t="n"/>
       <c r="F86" s="24" t="n"/>
       <c r="I86" s="33" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="23" t="inlineStr">
         <is>
-          <t>African Stone Bracelet Upper Volta River 2 0f 4</t>
+          <t>African Stone Bracelet Upper Volta River 1 0f 4</t>
         </is>
       </c>
       <c r="B87" s="32" t="inlineStr">
@@ -10339,7 +10344,7 @@
     <row r="88">
       <c r="A88" s="23" t="inlineStr">
         <is>
-          <t>African Stone Bracelet Upper Volta River 4 0f 4</t>
+          <t>African Stone Bracelet Upper Volta River 2 0f 4</t>
         </is>
       </c>
       <c r="B88" s="32" t="inlineStr">
@@ -10359,19 +10364,19 @@
     <row r="89">
       <c r="A89" s="23" t="inlineStr">
         <is>
-          <t>A Saharan Stone Discoidal</t>
+          <t>African Stone Bracelet Upper Volta River 4 0f 4</t>
         </is>
       </c>
       <c r="B89" s="32" t="inlineStr">
         <is>
-          <t>Pace African Art</t>
+          <t>Live Auctioneers</t>
         </is>
       </c>
       <c r="C89" s="24" t="n">
-        <v>1000</v>
+        <v>293</v>
       </c>
       <c r="D89" s="39" t="n">
-        <v>44562</v>
+        <v>44548</v>
       </c>
       <c r="F89" s="24" t="n"/>
       <c r="I89" s="33" t="n"/>
@@ -10379,16 +10384,19 @@
     <row r="90">
       <c r="A90" s="23" t="inlineStr">
         <is>
-          <t>Carved Ostrish Egg</t>
+          <t>A Saharan Stone Discoidal</t>
         </is>
       </c>
       <c r="B90" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Etsy </t>
+          <t>Pace African Art</t>
         </is>
       </c>
       <c r="C90" s="24" t="n">
-        <v>90</v>
+        <v>1000</v>
+      </c>
+      <c r="D90" s="39" t="n">
+        <v>44562</v>
       </c>
       <c r="F90" s="24" t="n"/>
       <c r="I90" s="33" t="n"/>
@@ -10396,16 +10404,16 @@
     <row r="91">
       <c r="A91" s="23" t="inlineStr">
         <is>
-          <t>Carved Goose Egg</t>
+          <t>Carved Ostrish Egg</t>
         </is>
       </c>
       <c r="B91" s="32" t="inlineStr">
         <is>
-          <t>Etsy</t>
+          <t xml:space="preserve">Etsy </t>
         </is>
       </c>
       <c r="C91" s="24" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="F91" s="24" t="n"/>
       <c r="I91" s="33" t="n"/>
@@ -10422,7 +10430,7 @@
         </is>
       </c>
       <c r="C92" s="24" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F92" s="24" t="n"/>
       <c r="I92" s="33" t="n"/>
@@ -10430,31 +10438,29 @@
     <row r="93">
       <c r="A93" s="23" t="inlineStr">
         <is>
-          <t>Quimbaya Figure (Gift)</t>
+          <t>Carved Goose Egg</t>
         </is>
       </c>
       <c r="B93" s="32" t="inlineStr">
         <is>
-          <t>Jeffrey Norris</t>
+          <t>Etsy</t>
         </is>
       </c>
       <c r="C93" s="24" t="n">
-        <v>10</v>
-      </c>
-      <c r="D93" s="39" t="n">
-        <v>45079</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="F93" s="24" t="n"/>
       <c r="I93" s="33" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="23" t="inlineStr">
         <is>
-          <t>A Saharan Stone Discoidal (Gift)</t>
+          <t>Quimbaya Figure (Gift)</t>
         </is>
       </c>
       <c r="B94" s="32" t="inlineStr">
         <is>
-          <t>Aquinas Hobor</t>
+          <t>Jeffrey Norris</t>
         </is>
       </c>
       <c r="C94" s="24" t="n">
@@ -10468,7 +10474,7 @@
     <row r="95">
       <c r="A95" s="23" t="inlineStr">
         <is>
-          <t>A Saharan Stone Discoidal</t>
+          <t>A Saharan Stone Discoidal (Gift)</t>
         </is>
       </c>
       <c r="B95" s="32" t="inlineStr">
@@ -10476,31 +10482,30 @@
           <t>Aquinas Hobor</t>
         </is>
       </c>
-      <c r="C95" s="43" t="n">
-        <v>500</v>
+      <c r="C95" s="24" t="n">
+        <v>10</v>
       </c>
       <c r="D95" s="39" t="n">
         <v>45079</v>
       </c>
-      <c r="F95" s="24" t="n"/>
       <c r="I95" s="33" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="23" t="inlineStr">
         <is>
-          <t>Two Songye and Bozo Vessels</t>
+          <t>A Saharan Stone Discoidal</t>
         </is>
       </c>
       <c r="B96" s="32" t="inlineStr">
         <is>
-          <t>Hindman</t>
+          <t>Aquinas Hobor</t>
         </is>
       </c>
       <c r="C96" s="43" t="n">
-        <v>138.91</v>
+        <v>500</v>
       </c>
       <c r="D96" s="39" t="n">
-        <v>45211</v>
+        <v>45079</v>
       </c>
       <c r="F96" s="24" t="n"/>
       <c r="I96" s="33" t="n"/>
@@ -10508,19 +10513,19 @@
     <row r="97">
       <c r="A97" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sword 9th Century </t>
+          <t>Two Songye and Bozo Vessels</t>
         </is>
       </c>
       <c r="B97" s="32" t="inlineStr">
         <is>
-          <t>Zevantiques</t>
+          <t>Hindman</t>
         </is>
       </c>
       <c r="C97" s="43" t="n">
-        <v>3000</v>
+        <v>138.91</v>
       </c>
       <c r="D97" s="39" t="n">
-        <v>45311</v>
+        <v>45211</v>
       </c>
       <c r="F97" s="24" t="n"/>
       <c r="I97" s="33" t="n"/>
@@ -10528,19 +10533,19 @@
     <row r="98">
       <c r="A98" s="23" t="inlineStr">
         <is>
-          <t>A Roman Marble Plaque with Insciption</t>
+          <t xml:space="preserve">Sword 9th Century </t>
         </is>
       </c>
       <c r="B98" s="32" t="inlineStr">
         <is>
-          <t>ebay</t>
+          <t>Zevantiques</t>
         </is>
       </c>
       <c r="C98" s="43" t="n">
-        <v>1331.41</v>
+        <v>3000</v>
       </c>
       <c r="D98" s="39" t="n">
-        <v>45546</v>
+        <v>45311</v>
       </c>
       <c r="F98" s="24" t="n"/>
       <c r="I98" s="33" t="n"/>
@@ -10548,7 +10553,7 @@
     <row r="99">
       <c r="A99" s="23" t="inlineStr">
         <is>
-          <t>Erotic Intaglio Finger Ring</t>
+          <t>A Roman Marble Plaque with Insciption</t>
         </is>
       </c>
       <c r="B99" s="32" t="inlineStr">
@@ -10557,73 +10562,82 @@
         </is>
       </c>
       <c r="C99" s="43" t="n">
-        <v>205.07</v>
+        <v>1331.41</v>
       </c>
       <c r="D99" s="39" t="n">
-        <v>45446</v>
+        <v>45546</v>
       </c>
       <c r="F99" s="24" t="n"/>
       <c r="I99" s="33" t="n"/>
     </row>
     <row r="100">
-      <c r="B100" s="32" t="n"/>
-      <c r="C100" s="43" t="n"/>
-      <c r="D100" s="39" t="n"/>
+      <c r="A100" s="23" t="inlineStr">
+        <is>
+          <t>Erotic Intaglio Finger Ring</t>
+        </is>
+      </c>
+      <c r="B100" s="32" t="inlineStr">
+        <is>
+          <t>ebay</t>
+        </is>
+      </c>
+      <c r="C100" s="43" t="n">
+        <v>205.07</v>
+      </c>
+      <c r="D100" s="39" t="n">
+        <v>45446</v>
+      </c>
       <c r="F100" s="24" t="n"/>
       <c r="I100" s="33" t="n"/>
     </row>
     <row r="101">
-      <c r="A101" s="21" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
       <c r="B101" s="32" t="n"/>
-      <c r="C101" s="26" t="n"/>
+      <c r="C101" s="43" t="n"/>
+      <c r="D101" s="39" t="n"/>
       <c r="F101" s="24" t="n"/>
       <c r="I101" s="33" t="n"/>
     </row>
     <row r="102">
+      <c r="A102" s="21" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="B102" s="32" t="n"/>
-      <c r="C102" s="24" t="n"/>
+      <c r="C102" s="26" t="n"/>
       <c r="F102" s="24" t="n"/>
       <c r="I102" s="33" t="n"/>
     </row>
     <row r="103">
-      <c r="A103" s="21" t="inlineStr">
-        <is>
-          <t>Office/Business Inventory</t>
-        </is>
-      </c>
       <c r="B103" s="32" t="n"/>
       <c r="C103" s="24" t="n"/>
-      <c r="D103" s="57" t="n"/>
-      <c r="E103" s="57" t="n"/>
       <c r="F103" s="24" t="n"/>
-      <c r="G103" s="57" t="n"/>
-      <c r="H103" s="57" t="n"/>
       <c r="I103" s="33" t="n"/>
-      <c r="J103" s="57" t="n"/>
-      <c r="K103" s="57" t="n"/>
-      <c r="L103" s="57" t="n"/>
-      <c r="M103" s="57" t="n"/>
-      <c r="N103" s="57" t="n"/>
     </row>
     <row r="104">
-      <c r="A104" s="23" t="inlineStr">
-        <is>
-          <t>Sofa</t>
+      <c r="A104" s="21" t="inlineStr">
+        <is>
+          <t>Office/Business Inventory</t>
         </is>
       </c>
       <c r="B104" s="32" t="n"/>
       <c r="C104" s="24" t="n"/>
+      <c r="D104" s="60" t="n"/>
+      <c r="E104" s="60" t="n"/>
       <c r="F104" s="24" t="n"/>
+      <c r="G104" s="60" t="n"/>
+      <c r="H104" s="60" t="n"/>
       <c r="I104" s="33" t="n"/>
+      <c r="J104" s="60" t="n"/>
+      <c r="K104" s="60" t="n"/>
+      <c r="L104" s="60" t="n"/>
+      <c r="M104" s="60" t="n"/>
+      <c r="N104" s="60" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="23" t="inlineStr">
         <is>
-          <t>Space Heater</t>
+          <t>Sofa</t>
         </is>
       </c>
       <c r="B105" s="32" t="n"/>
@@ -10634,7 +10648,7 @@
     <row r="106">
       <c r="A106" s="23" t="inlineStr">
         <is>
-          <t>Shelving</t>
+          <t>Space Heater</t>
         </is>
       </c>
       <c r="B106" s="32" t="n"/>
@@ -10645,7 +10659,7 @@
     <row r="107">
       <c r="A107" s="23" t="inlineStr">
         <is>
-          <t>Storage Bins</t>
+          <t>Shelving</t>
         </is>
       </c>
       <c r="B107" s="32" t="n"/>
@@ -10656,7 +10670,7 @@
     <row r="108">
       <c r="A108" s="23" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Storage Bins</t>
         </is>
       </c>
       <c r="B108" s="32" t="n"/>
@@ -10667,7 +10681,7 @@
     <row r="109">
       <c r="A109" s="23" t="inlineStr">
         <is>
-          <t>Computer</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="B109" s="32" t="n"/>
@@ -10678,7 +10692,7 @@
     <row r="110">
       <c r="A110" s="23" t="inlineStr">
         <is>
-          <t>Art Library</t>
+          <t>Computer</t>
         </is>
       </c>
       <c r="B110" s="32" t="n"/>
@@ -10689,7 +10703,7 @@
     <row r="111">
       <c r="A111" s="23" t="inlineStr">
         <is>
-          <t>Standing Desk</t>
+          <t>Art Library</t>
         </is>
       </c>
       <c r="B111" s="32" t="n"/>
@@ -10698,46 +10712,37 @@
       <c r="I111" s="33" t="n"/>
     </row>
     <row r="112">
+      <c r="A112" s="23" t="inlineStr">
+        <is>
+          <t>Standing Desk</t>
+        </is>
+      </c>
       <c r="B112" s="32" t="n"/>
       <c r="C112" s="24" t="n"/>
       <c r="F112" s="24" t="n"/>
       <c r="I112" s="33" t="n"/>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="inlineStr">
-        <is>
-          <t>2025 CC inventory (not in Cost total until object is named)</t>
-        </is>
-      </c>
       <c r="B113" s="32" t="n"/>
       <c r="C113" s="24" t="n"/>
       <c r="F113" s="24" t="n"/>
       <c r="I113" s="33" t="n"/>
     </row>
     <row r="114">
-      <c r="A114" s="49" t="inlineStr">
-        <is>
-          <t>Los Angeles Modern Auctions (inventory purchase)</t>
-        </is>
-      </c>
-      <c r="B114" s="49" t="inlineStr">
-        <is>
-          <t>Sapphire 5423</t>
-        </is>
-      </c>
-      <c r="C114" s="58" t="n">
-        <v>6821.06</v>
-      </c>
-      <c r="D114" s="49" t="inlineStr">
-        <is>
-          <t>2025-07-24</t>
-        </is>
-      </c>
+      <c r="A114" s="1" t="inlineStr">
+        <is>
+          <t>2025 CC inventory (not in Cost total until object is named)</t>
+        </is>
+      </c>
+      <c r="B114" s="32" t="n"/>
+      <c r="C114" s="24" t="n"/>
+      <c r="F114" s="24" t="n"/>
+      <c r="I114" s="33" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="49" t="inlineStr">
         <is>
-          <t>Hindman LLC (inventory purchase)</t>
+          <t>Los Angeles Modern Auctions (inventory purchase)</t>
         </is>
       </c>
       <c r="B115" s="49" t="inlineStr">
@@ -10745,12 +10750,12 @@
           <t>Sapphire 5423</t>
         </is>
       </c>
-      <c r="C115" s="58" t="n">
-        <v>282.24</v>
+      <c r="C115" s="61" t="n">
+        <v>6821.06</v>
       </c>
       <c r="D115" s="49" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-07-24</t>
         </is>
       </c>
     </row>
@@ -10765,295 +10770,274 @@
           <t>Sapphire 5423</t>
         </is>
       </c>
-      <c r="C116" s="58" t="n">
-        <v>403.51</v>
+      <c r="C116" s="61" t="n">
+        <v>282.24</v>
       </c>
       <c r="D116" s="49" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-04-03</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="49" t="inlineStr">
         <is>
+          <t>Hindman LLC (inventory purchase)</t>
+        </is>
+      </c>
+      <c r="B117" s="49" t="inlineStr">
+        <is>
+          <t>Sapphire 5423</t>
+        </is>
+      </c>
+      <c r="C117" s="61" t="n">
+        <v>403.51</v>
+      </c>
+      <c r="D117" s="49" t="inlineStr">
+        <is>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="49" t="inlineStr">
+        <is>
           <t>The Great Frame Up (inventory framing)</t>
         </is>
       </c>
-      <c r="B117" s="49" t="inlineStr">
+      <c r="B118" s="49" t="inlineStr">
         <is>
           <t>Sapphire 5423</t>
         </is>
       </c>
-      <c r="C117" s="58" t="n">
+      <c r="C118" s="61" t="n">
         <v>536.41</v>
       </c>
-      <c r="D117" s="49" t="inlineStr">
+      <c r="D118" s="49" t="inlineStr">
         <is>
           <t>2025-02-16</t>
         </is>
       </c>
     </row>
-    <row r="118"/>
-    <row r="119">
-      <c r="A119" s="59" t="inlineStr">
+    <row r="119"/>
+    <row r="120">
+      <c r="A120" s="62" t="inlineStr">
         <is>
           <t>2025 Mercury 8291 — David Aaron Limited is LOCKED consultant fee (not Art Sales)</t>
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="7" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="7" t="inlineStr">
         <is>
           <t>NOT a 2025 art sale — David Aaron Limited consultant fee (EPGC Consultant June)</t>
         </is>
       </c>
-      <c r="B120" s="7" t="inlineStr">
+      <c r="B121" s="7" t="inlineStr">
         <is>
           <t>David Aaron Limited</t>
         </is>
       </c>
-      <c r="C120" s="7" t="n"/>
-      <c r="D120" s="7" t="n"/>
-      <c r="E120" s="7" t="n"/>
-      <c r="F120" s="14" t="n"/>
-      <c r="G120" s="60" t="n"/>
-      <c r="H120" s="60" t="n"/>
-      <c r="I120" s="7" t="inlineStr">
+      <c r="C121" s="7" t="n"/>
+      <c r="D121" s="7" t="n"/>
+      <c r="E121" s="7" t="n"/>
+      <c r="F121" s="14" t="n"/>
+      <c r="G121" s="63" t="n"/>
+      <c r="H121" s="63" t="n"/>
+      <c r="I121" s="7" t="inlineStr">
         <is>
           <t>LOCKED 2026-09-20: consultant fee, not a sale. $13,595 is on EPGC Consultant June. Not tax advice.</t>
         </is>
       </c>
     </row>
-    <row r="121"/>
-    <row r="122">
-      <c r="A122" s="59" t="inlineStr">
+    <row r="122"/>
+    <row r="123">
+      <c r="A123" s="62" t="inlineStr">
         <is>
           <t>2025 Mercury COGS — Newstar Jewelers (LOCKED jewelry fabrication)</t>
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="61" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="64" t="inlineStr">
         <is>
           <t>Newstar Jewelers — jewelry from intaglios / engraved gems / scarabs</t>
         </is>
       </c>
-      <c r="B123" s="61" t="inlineStr">
+      <c r="B124" s="64" t="inlineStr">
         <is>
           <t>Mercury 8291</t>
         </is>
       </c>
-      <c r="C123" s="62" t="n">
+      <c r="C124" s="65" t="n">
         <v>8000</v>
       </c>
-      <c r="D123" s="61" t="inlineStr">
+      <c r="D124" s="64" t="inlineStr">
         <is>
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="I123" s="49" t="inlineStr">
+      <c r="I124" s="49" t="inlineStr">
         <is>
           <t>LOCKED COGS fabrication. Not in sold-lot Cost total (Feb Berk lots already sold). Identify which gems/intaglios/scarabs.</t>
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="61" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="64" t="inlineStr">
         <is>
           <t>Newstar Jewelers — jewelry from intaglios / engraved gems / scarabs</t>
         </is>
       </c>
-      <c r="B124" s="61" t="inlineStr">
+      <c r="B125" s="64" t="inlineStr">
         <is>
           <t>Mercury 8291</t>
         </is>
       </c>
-      <c r="C124" s="62" t="n">
+      <c r="C125" s="65" t="n">
         <v>8000</v>
       </c>
-      <c r="D124" s="61" t="inlineStr">
+      <c r="D125" s="64" t="inlineStr">
         <is>
           <t>2025-11-12</t>
         </is>
       </c>
-      <c r="I124" s="49" t="inlineStr">
+      <c r="I125" s="49" t="inlineStr">
         <is>
           <t>LOCKED COGS fabrication. Not in sold-lot Cost total (Feb Berk lots already sold). Identify which gems/intaglios/scarabs.</t>
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="61" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="64" t="inlineStr">
         <is>
           <t>Newstar Jewelers — jewelry from intaglios / engraved gems / scarabs (3 of 3)</t>
         </is>
       </c>
-      <c r="B125" s="61" t="inlineStr">
+      <c r="B126" s="64" t="inlineStr">
         <is>
           <t>Mercury 8291</t>
         </is>
       </c>
-      <c r="C125" s="62" t="n">
+      <c r="C126" s="65" t="n">
         <v>7581</v>
       </c>
-      <c r="D125" s="61" t="inlineStr">
+      <c r="D126" s="64" t="inlineStr">
         <is>
           <t>2025-12-24</t>
         </is>
       </c>
-      <c r="I125" s="49" t="inlineStr">
+      <c r="I126" s="49" t="inlineStr">
         <is>
           <t>LOCKED COGS fabrication. Not in sold-lot Cost total (Feb Berk lots already sold). Identify which gems/intaglios/scarabs.</t>
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="49" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="49" t="inlineStr">
         <is>
           <t>Newstar 2025 total</t>
         </is>
       </c>
-      <c r="C126" s="62">
+      <c r="C127" s="65">
         <f>SUM(C123:C125)</f>
         <v/>
       </c>
     </row>
-    <row r="127"/>
-    <row r="128">
-      <c r="A128" s="63" t="inlineStr">
+    <row r="128"/>
+    <row r="129">
+      <c r="A129" s="66" t="inlineStr">
         <is>
           <t>2025 Mercury ASK — Fortuna inventory remaining (not in Cost total until object is named)</t>
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="64" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="56" t="inlineStr">
         <is>
           <t>Fortuna / Erdal Dere — object TBD</t>
         </is>
       </c>
-      <c r="B129" s="64" t="inlineStr">
+      <c r="B130" s="56" t="inlineStr">
         <is>
           <t>Mercury 8291</t>
         </is>
       </c>
-      <c r="C129" s="58" t="n">
+      <c r="C130" s="61" t="n">
         <v>20000</v>
       </c>
-      <c r="D129" s="64" t="inlineStr">
+      <c r="D130" s="56" t="inlineStr">
         <is>
           <t>2025-05-09</t>
         </is>
       </c>
-      <c r="I129" s="49" t="inlineStr">
+      <c r="I130" s="49" t="inlineStr">
         <is>
           <t>ASK: inventory purchase vs other. Do not add to sold Cost until named (avoid double count).</t>
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="64" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="56" t="inlineStr">
         <is>
           <t>Fortuna / Erdal Dere — object TBD</t>
         </is>
       </c>
-      <c r="B130" s="64" t="inlineStr">
+      <c r="B131" s="56" t="inlineStr">
         <is>
           <t>Mercury 8291</t>
         </is>
       </c>
-      <c r="C130" s="58" t="n">
+      <c r="C131" s="61" t="n">
         <v>45000</v>
       </c>
-      <c r="D130" s="64" t="inlineStr">
+      <c r="D131" s="56" t="inlineStr">
         <is>
           <t>2025-07-21</t>
         </is>
       </c>
-      <c r="I130" s="49" t="inlineStr">
+      <c r="I131" s="49" t="inlineStr">
         <is>
           <t>ASK: inventory purchase vs other. Do not add to sold Cost until named (avoid double count).</t>
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="64" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="56" t="inlineStr">
         <is>
           <t>Fortuna / Erdal Dere — object TBD</t>
         </is>
       </c>
-      <c r="B131" s="64" t="inlineStr">
+      <c r="B132" s="56" t="inlineStr">
         <is>
           <t>Mercury 8291</t>
         </is>
       </c>
-      <c r="C131" s="58" t="n">
+      <c r="C132" s="61" t="n">
         <v>20000</v>
       </c>
-      <c r="D131" s="64" t="inlineStr">
+      <c r="D132" s="56" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="I131" s="49" t="inlineStr">
+      <c r="I132" s="49" t="inlineStr">
         <is>
           <t>ASK: inventory purchase vs other. Do not add to sold Cost until named (avoid double count).</t>
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="49" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="49" t="inlineStr">
         <is>
           <t>Fortuna remaining 2025 (excl. seals $13,000 already on row 73)</t>
         </is>
       </c>
-      <c r="C132" s="58" t="n">
+      <c r="C133" s="61" t="n">
         <v>85000</v>
       </c>
     </row>
-    <row r="133"/>
-    <row r="134">
-      <c r="A134" s="59" t="inlineStr">
-        <is>
-          <t>2025 Mercury 8291 — Books sold to Aquinas Hobor (LOCKED)</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="7" t="inlineStr">
-        <is>
-          <t>Books sold to Aquinas Hobor (titles TBD)</t>
-        </is>
-      </c>
-      <c r="B135" s="7" t="inlineStr">
-        <is>
-          <t>Aquinas Hobor</t>
-        </is>
-      </c>
-      <c r="C135" s="7" t="n"/>
-      <c r="D135" s="7" t="n"/>
-      <c r="E135" s="7" t="inlineStr">
-        <is>
-          <t>Aquinas Hobor</t>
-        </is>
-      </c>
-      <c r="F135" s="14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G135" s="65" t="n">
-        <v>45692</v>
-      </c>
-      <c r="H135" s="7">
-        <f>IF(C135="","",F135-C135)</f>
-        <v/>
-      </c>
-      <c r="I135" s="7" t="inlineStr">
-        <is>
-          <t>LOCKED 2026-09-20: books sold to Aquinas. $1,000 cash on EPGC Art Sales February. Cost / titles TBD — not in Income I8 until Cost. Distinct from 2022 Saharan bracelets. Not tax advice.</t>
-        </is>
-      </c>
-    </row>
+    <row r="134"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11123,7 +11107,7 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="66" t="inlineStr">
+      <c r="A5" s="67" t="inlineStr">
         <is>
           <t>Coinbase (ACH from Mercury 8291)</t>
         </is>
@@ -11232,19 +11216,19 @@
       <c r="I7" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="67" t="n">
+      <c r="J7" s="68" t="n">
         <v>-9000</v>
       </c>
-      <c r="K7" s="67" t="n">
+      <c r="K7" s="68" t="n">
         <v>-10000</v>
       </c>
-      <c r="L7" s="67" t="n">
+      <c r="L7" s="68" t="n">
         <v>-35000</v>
       </c>
-      <c r="M7" s="67" t="n">
+      <c r="M7" s="68" t="n">
         <v>-5000</v>
       </c>
-      <c r="N7" s="68">
+      <c r="N7" s="69">
         <f>SUM(B7:M7)</f>
         <v/>
       </c>
@@ -11288,10 +11272,10 @@
       <c r="L8" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="M8" s="67" t="n">
+      <c r="M8" s="68" t="n">
         <v>8000</v>
       </c>
-      <c r="N8" s="68">
+      <c r="N8" s="69">
         <f>SUM(B8:M8)</f>
         <v/>
       </c>
@@ -11338,14 +11322,14 @@
       <c r="M9" s="14" t="n">
         <v>3000</v>
       </c>
-      <c r="N9" s="68">
+      <c r="N9" s="69">
         <f>SUM(B9:M9)</f>
         <v/>
       </c>
     </row>
     <row r="10"/>
     <row r="11">
-      <c r="A11" s="69" t="inlineStr">
+      <c r="A11" s="70" t="inlineStr">
         <is>
           <t>2025: funded $59,000.00 / returned $8,000.00 / net $-51,000.00 off the EPGC operating account. Not income, not an expense. Not tax advice.</t>
         </is>
@@ -11378,28 +11362,28 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="57" t="n">
+      <c r="B1" s="60" t="n">
         <v>2022</v>
       </c>
       <c r="C1" s="23" t="n">
         <v>2022</v>
       </c>
-      <c r="D1" s="57" t="n">
+      <c r="D1" s="60" t="n">
         <v>2023</v>
       </c>
       <c r="E1" s="23" t="n">
         <v>2023</v>
       </c>
-      <c r="F1" s="57" t="n">
+      <c r="F1" s="60" t="n">
         <v>2024</v>
       </c>
       <c r="G1" s="23" t="n">
         <v>2024</v>
       </c>
-      <c r="H1" s="57" t="n">
+      <c r="H1" s="60" t="n">
         <v>2025</v>
       </c>
-      <c r="I1" s="57" t="n">
+      <c r="I1" s="60" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -11414,7 +11398,7 @@
           <t>Actual</t>
         </is>
       </c>
-      <c r="D2" s="57" t="inlineStr">
+      <c r="D2" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">Projected </t>
         </is>
@@ -11424,7 +11408,7 @@
           <t>Actual</t>
         </is>
       </c>
-      <c r="F2" s="57" t="inlineStr">
+      <c r="F2" s="60" t="inlineStr">
         <is>
           <t>Projected</t>
         </is>
@@ -11434,7 +11418,7 @@
           <t>Actual</t>
         </is>
       </c>
-      <c r="H2" s="57" t="inlineStr">
+      <c r="H2" s="60" t="inlineStr">
         <is>
           <t>Projected</t>
         </is>
@@ -11452,8 +11436,8 @@
         </is>
       </c>
       <c r="B3" s="24" t="n"/>
-      <c r="D3" s="57" t="n"/>
-      <c r="F3" s="57" t="n"/>
+      <c r="D3" s="60" t="n"/>
+      <c r="F3" s="60" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="23" t="inlineStr">
@@ -11473,11 +11457,11 @@
       <c r="E4" s="24" t="n">
         <v>115000</v>
       </c>
-      <c r="F4" s="70" t="n">
+      <c r="F4" s="71" t="n">
         <v>110000</v>
       </c>
-      <c r="G4" s="71" t="n"/>
-      <c r="H4" s="68" t="n">
+      <c r="G4" s="72" t="n"/>
+      <c r="H4" s="69" t="n">
         <v>110000</v>
       </c>
       <c r="I4" s="16" t="n">
@@ -11500,14 +11484,14 @@
         <v>1500</v>
       </c>
       <c r="E5" s="24" t="n"/>
-      <c r="F5" s="70" t="n">
+      <c r="F5" s="71" t="n">
         <v>1500</v>
       </c>
-      <c r="G5" s="71" t="n"/>
-      <c r="H5" s="68" t="n">
+      <c r="G5" s="72" t="n"/>
+      <c r="H5" s="69" t="n">
         <v>19500</v>
       </c>
-      <c r="I5" s="68" t="n">
+      <c r="I5" s="69" t="n">
         <v>19500</v>
       </c>
     </row>
@@ -11521,14 +11505,14 @@
       <c r="C6" s="24" t="n"/>
       <c r="D6" s="24" t="n"/>
       <c r="E6" s="24" t="n"/>
-      <c r="F6" s="70" t="n">
+      <c r="F6" s="71" t="n">
         <v>20000</v>
       </c>
-      <c r="G6" s="71" t="n"/>
-      <c r="H6" s="68" t="n">
+      <c r="G6" s="72" t="n"/>
+      <c r="H6" s="69" t="n">
         <v>17000</v>
       </c>
-      <c r="I6" s="68" t="n">
+      <c r="I6" s="69" t="n">
         <v>17086.94</v>
       </c>
     </row>
@@ -11550,14 +11534,14 @@
       <c r="E7" s="24" t="n">
         <v>14700</v>
       </c>
-      <c r="F7" s="70" t="n">
+      <c r="F7" s="71" t="n">
         <v>16000</v>
       </c>
-      <c r="G7" s="70" t="n"/>
-      <c r="H7" s="68" t="n">
+      <c r="G7" s="71" t="n"/>
+      <c r="H7" s="69" t="n">
         <v>21500</v>
       </c>
-      <c r="I7" s="68" t="n">
+      <c r="I7" s="69" t="n">
         <v>21500</v>
       </c>
     </row>
@@ -11579,11 +11563,11 @@
       <c r="E8" s="24" t="n">
         <v>54777.25</v>
       </c>
-      <c r="F8" s="70" t="n">
+      <c r="F8" s="71" t="n">
         <v>20000</v>
       </c>
-      <c r="G8" s="71" t="n"/>
-      <c r="H8" s="68" t="n">
+      <c r="G8" s="72" t="n"/>
+      <c r="H8" s="69" t="n">
         <v>20000</v>
       </c>
       <c r="I8" s="16" t="n">
@@ -11606,14 +11590,14 @@
         <v>74000</v>
       </c>
       <c r="E9" s="24" t="n"/>
-      <c r="F9" s="70" t="n">
+      <c r="F9" s="71" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="71" t="n"/>
-      <c r="H9" s="68" t="n">
+      <c r="G9" s="72" t="n"/>
+      <c r="H9" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="68" t="n">
+      <c r="I9" s="69" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11639,19 +11623,19 @@
         <f>SUM(E4:E9)</f>
         <v/>
       </c>
-      <c r="F10" s="70">
+      <c r="F10" s="71">
         <f>SUM(F4:F9)</f>
         <v/>
       </c>
-      <c r="G10" s="70">
+      <c r="G10" s="71">
         <f>SUM(G4:G9)</f>
         <v/>
       </c>
-      <c r="H10" s="70">
+      <c r="H10" s="71">
         <f>SUM(H4:H9)</f>
         <v/>
       </c>
-      <c r="I10" s="70">
+      <c r="I10" s="71">
         <f>SUM(I4:I9)</f>
         <v/>
       </c>
@@ -11661,7 +11645,7 @@
       <c r="B11" s="24" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="69" t="inlineStr">
+      <c r="A12" s="70" t="inlineStr">
         <is>
           <t>2025 Actual: I4 Monarch paycheck cash ≠ W-2 Box 1. I5 216 LTR cash $19,500. I6 524 #2 STR platform net LOCKED. I7 GCM 1099-NEC $21,500. I8 Art net $23,055.06 = MATCHED Mercury deals only (Berk lots $30,000 − $22,944.94 Cost) + seals $1,000 + mosaics $15,000. Excludes Sale 6428 $11,000 until Cost. Excludes Aquinas books $1,000 until Cost. David Aaron $13,595 is EPGC Consultant June (not I8). Erdal/Aysel/EOEB/L5 ASK. Not tax advice.</t>
         </is>

--- a/.cursor/scratch/tax_turbo_parts/Personal Income 2025 — Mercury 8291.xlsx
+++ b/.cursor/scratch/tax_turbo_parts/Personal Income 2025 — Mercury 8291.xlsx
@@ -169,7 +169,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -300,7 +300,6 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="12" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -674,7 +673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -729,12 +728,12 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>3. Fortuna / Erdal Dere OUT after seals</t>
+          <t>3. Fortuna / Erdal $20,000 Aug — object still unnamed</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>$85,000.00 after the 1/8 $13,000 seals COGS (5/9 $20k, 7/21 $45k, 8/15 $20k). Inventory purchases (object names) or something else?</t>
+          <t>$20,000.00. Monarch posted 8/15 = Mercury native initiated 8/18 (same cash, not a second unique txn). Native memo has no object name. Venus $20,000 (5/9) and Roman Gold Belt $45,000 (7/21) are LOCKED inventory below — not this question.</t>
         </is>
       </c>
     </row>
@@ -753,12 +752,12 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>5. Aysel Dere $50,000 IN (7/18)</t>
+          <t>5. Aysel Dere $50,000 — Monarch IN vs native Failed OUT</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>Sale, related-party transfer, or part of the mid-July Fortuna/L5 cluster?</t>
+          <t>Monarch 7/18 +$50,000 IN is in the 64. Mercury native CSV has NO Sent Aysel cash — only Failed $50,000 OUT 7/17 'Recipient account does not exist'. Is the Monarch IN a phantom of the failed send, or a real incoming the export omitted? Do not dump onto Art Sales or Consultant until confirmed.</t>
         </is>
       </c>
     </row>
@@ -971,6 +970,42 @@
       <c r="B27" s="9" t="inlineStr">
         <is>
           <t>CONFIRMED mixed art sales AND advisory/consultant. Remainder $130,270 / $87,396.32 unallocated — not on P&amp;L until invoice split. Jan 16 $1,000 Canosan-horse still open.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>Fortuna Venus inventory</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>$20,000 OUT 5/9 LOCKED. Mercury native note: bronze head of a goddess, likely Venus. Parked Cost — not sold 2025, not dumped onto Art Sales/Consultant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>Fortuna Roman Gold Belt</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>$45,000 OUT 7/21 LOCKED. Mercury native note: Roman Gold Belt. Parked Cost — not sold 2025, not dumped onto Art Sales/Consultant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>Native CSV 2026-09-20</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>epgc-llc-transactions-2025-jan-01-to-2025-dec-31.csv is account 8291, same 2025 year already classified. 0 new unique Sent cash vs the 64. Failed Aysel 7/17 and Cancelled Erdal 1/8 are not cash.</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1041,7 @@
     <row r="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>Mercury Checking 8291 — EPGC LLC (Choice Financial) 2025. 64 unique cash transactions. Coinbase ACH = investment. Newstar = jewelry COGS on intaglios/gems/scarabs. BoA 9922 draws and Koziol/Ariadne $150k are LOCKED not-P&amp;L (pass-through / owner transfer). David Aaron $13,595 is LOCKED EPGC Consultant (June). Wise $334.17 + $658.63 are LOCKED EPGC Consultant Fees (expertise write-ups). Aquinas Hobor $1,000 (2/4) is LOCKED books sold (EPGC Art Sales February; Cost TBD). Not tax advice.</t>
+          <t>Mercury Checking 8291 — EPGC LLC (Choice Financial) 2025. 64 unique cash transactions (Monarch IDs). Native Mercury CSV 2026-09-20 is the same 8291 year — 0 new unique Sent cash. Coinbase ACH = investment. Newstar = jewelry COGS on intaglios/gems/scarabs. Fortuna Venus $20k (5/9) + Roman Gold Belt $45k (7/21) LOCKED inventory (not sold Cost). BoA 9922 draws and Koziol/Ariadne $150k are LOCKED not-P&amp;L (pass-through / owner transfer). David Aaron $13,595 is LOCKED EPGC Consultant (June). Wise $334.17 + $658.63 are LOCKED EPGC Consultant Fees (expertise write-ups). Aquinas Hobor $1,000 (2/4) is LOCKED books sold (EPGC Art Sales February; Cost TBD). Not tax advice.</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1159,12 @@
       </c>
       <c r="K4" s="12" t="inlineStr">
         <is>
-          <t>Merchant name: Erdal Dere (Fortuna)</t>
+          <t>Merchant name: Erdal Dere (Fortuna); Mercury native: J.K. New York Collection | Send Money transaction initiated on Mercury</t>
         </is>
       </c>
       <c r="L4" s="15" t="inlineStr">
         <is>
-          <t>Fortuna / Erdal Dere. Matches Art Sales Cost $13,000; Berk sold it 1/10 for $14,000.</t>
+          <t>Fortuna / Erdal Dere. Mercury native note: J.K. New York Collection. Matches Art Sales Cost $13,000; Berk sold it 1/10 for $14,000. Same-day Cancelled ACH to Erdal Dere (closed) is not cash.</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1519,7 @@
       </c>
       <c r="K10" s="12" t="inlineStr">
         <is>
-          <t>Merchant name: Jamal M Rifai</t>
+          <t>Merchant name: Jamal M Rifai; Mercury native: via mercury.com | Send Money transaction initiated on Mercury</t>
         </is>
       </c>
       <c r="L10" s="15" t="inlineStr">
@@ -1724,7 +1759,7 @@
       </c>
       <c r="K14" s="12" t="inlineStr">
         <is>
-          <t>Merchant name: Jamal M Rifai</t>
+          <t>Merchant name: Jamal M Rifai; Mercury native: From EPGC LLC via mercury.com | Send Money transaction initiated on Mercury</t>
         </is>
       </c>
       <c r="L14" s="15" t="inlineStr">
@@ -1784,7 +1819,7 @@
       </c>
       <c r="K15" s="12" t="inlineStr">
         <is>
-          <t>Merchant name: Plutus &amp; Mnemosyne, LLC</t>
+          <t>Merchant name: Plutus &amp; Mnemosyne, LLC; Mercury native: via mercury.com | Send Money transaction initiated on Mercury</t>
         </is>
       </c>
       <c r="L15" s="15" t="inlineStr">
@@ -1904,7 +1939,7 @@
       </c>
       <c r="K17" s="12" t="inlineStr">
         <is>
-          <t>Merchant name: Plutus &amp; Mnemosyne, LLC</t>
+          <t>Merchant name: Plutus &amp; Mnemosyne, LLC; Mercury native: From EPGC LLC via mercury.com | Send Money transaction initiated on Mercury</t>
         </is>
       </c>
       <c r="L17" s="15" t="inlineStr">
@@ -2044,7 +2079,7 @@
           <t>Erdal Dere (Fortuna)</t>
         </is>
       </c>
-      <c r="C20" s="18" t="n">
+      <c r="C20" s="13" t="n">
         <v>-20000</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
@@ -2057,14 +2092,14 @@
           <t>ART_PURCHASE</t>
         </is>
       </c>
-      <c r="F20" s="19" t="inlineStr">
-        <is>
-          <t>ASK</t>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>LOCKED</t>
         </is>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
-          <t>Fortuna / Erdal — inventory vs other</t>
+          <t>Bronze head of a goddess, likely Venus — inventory Cost</t>
         </is>
       </c>
       <c r="H20" s="12" t="inlineStr">
@@ -2084,12 +2119,12 @@
       </c>
       <c r="K20" s="12" t="inlineStr">
         <is>
-          <t>Merchant name: Erdal Dere (Fortuna)</t>
+          <t>Merchant name: Erdal Dere (Fortuna); Mercury native: For bronze head of a goddess, likely Venus | Send Money transaction initiated on Mercury</t>
         </is>
       </c>
       <c r="L20" s="15" t="inlineStr">
         <is>
-          <t>After seals $13,000. Object name? Inventory purchase (COGS when sold) or something else?</t>
+          <t>Mercury native 2025 CSV note: 'For bronze head of a goddess, likely Venus'. Inventory purchase from Fortuna / Erdal. Not sold on 2025 Art Sales — parked Cost, not in sold-lot Cost (avoid double count). Not dumped onto Consultant or Art Sales P&amp;L.</t>
         </is>
       </c>
     </row>
@@ -2724,7 +2759,7 @@
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>Aysel Dere $50,000 IN</t>
+          <t>Aysel Dere $50,000 IN on Monarch — NOT on Mercury native Sent</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
@@ -2749,7 +2784,7 @@
       </c>
       <c r="L31" s="15" t="inlineStr">
         <is>
-          <t>Same week as L5 $50k, Fortuna $45k OUT (7/21), Erdal $26k IN (7/24). Sale, family/related transfer, or inventory reverse?</t>
+          <t>Monarch 7/18 +$50,000 IN. Mercury native 2025 CSV (user upload 2026-09-20) has no Sent Aysel cash. Native has Failed $50,000 OUT 7/17 'Recipient account does not exist'. Keep on ASK — do not dump onto Art Sales or Consultant. Is the Monarch IN a phantom of the failed send?</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2799,7 @@
           <t>Erdal Dere (Fortuna)</t>
         </is>
       </c>
-      <c r="C32" s="18" t="n">
+      <c r="C32" s="13" t="n">
         <v>-45000</v>
       </c>
       <c r="D32" s="12" t="inlineStr">
@@ -2777,14 +2812,14 @@
           <t>ART_PURCHASE</t>
         </is>
       </c>
-      <c r="F32" s="19" t="inlineStr">
-        <is>
-          <t>ASK</t>
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t>LOCKED</t>
         </is>
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
-          <t>Fortuna / Erdal — inventory vs other</t>
+          <t>Roman Gold Belt — inventory Cost</t>
         </is>
       </c>
       <c r="H32" s="12" t="inlineStr">
@@ -2804,12 +2839,12 @@
       </c>
       <c r="K32" s="12" t="inlineStr">
         <is>
-          <t>Merchant name: Erdal Dere (Fortuna)</t>
+          <t>Merchant name: Erdal Dere (Fortuna); Mercury native: From EPGC LLC via mercury.com | Roman Gold Belt | Send Money transaction initiated on Mercury</t>
         </is>
       </c>
       <c r="L32" s="15" t="inlineStr">
         <is>
-          <t>Object name? Ties to Aysel $50k / Erdal $26k the same week?</t>
+          <t>Mercury native 2025 CSV note: Roman Gold Belt. Inventory purchase from Fortuna / Erdal. Not sold on 2025 Art Sales — parked Cost, not in sold-lot Cost. Same week as L5 $50k / Monarch Aysel $50k ASK / Erdal $26k IN.</t>
         </is>
       </c>
     </row>
@@ -2964,7 +2999,7 @@
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
-          <t>Fortuna / Erdal — inventory vs other</t>
+          <t>Fortuna / Erdal — object still unnamed</t>
         </is>
       </c>
       <c r="H35" s="12" t="inlineStr">
@@ -2984,12 +3019,12 @@
       </c>
       <c r="K35" s="12" t="inlineStr">
         <is>
-          <t>Merchant name: Erdal Dere (Fortuna)</t>
+          <t>Merchant name: Erdal Dere (Fortuna); Mercury native: From EPGC LLC via mercury.com | Send Money transaction initiated on Mercury</t>
         </is>
       </c>
       <c r="L35" s="15" t="inlineStr">
         <is>
-          <t>Object name?</t>
+          <t>Same $20,000 OUT as Mercury native initiated 2025-08-18 / Monarch posted 2025-08-15. No object name in the native memo ('From EPGC LLC via mercury.com'). Inventory vs other? Do not add to sold Cost until named. Not a second unique txn.</t>
         </is>
       </c>
     </row>
@@ -3764,7 +3799,7 @@
       </c>
       <c r="K48" s="12" t="inlineStr">
         <is>
-          <t>Merchant name: Newstar Jewelers</t>
+          <t>Merchant name: Newstar Jewelers; Mercury native: From EPGC LLC via mercury.com | 1 of 3 payments | Send Money transaction initiated on Mercury</t>
         </is>
       </c>
       <c r="L48" s="15" t="inlineStr">
@@ -3944,7 +3979,7 @@
       </c>
       <c r="K51" s="12" t="inlineStr">
         <is>
-          <t>Merchant name: Ariadne Demirjian LLC</t>
+          <t>Merchant name: Ariadne Demirjian LLC; Mercury native: via mercury.com; Vendor: Ariadne Demirjian LLC Roth 401k Account 5386-8600 | Send Money transaction initiated on Mercury</t>
         </is>
       </c>
       <c r="L51" s="15" t="inlineStr">
@@ -4364,7 +4399,7 @@
       </c>
       <c r="K58" s="12" t="inlineStr">
         <is>
-          <t>Merchant name: Newstar Jewelers</t>
+          <t>Merchant name: Newstar Jewelers; Mercury native: From EPGC LLC via mercury.com | Send Money transaction initiated on Mercury</t>
         </is>
       </c>
       <c r="L58" s="15" t="inlineStr">
@@ -4904,7 +4939,7 @@
       </c>
       <c r="K67" s="12" t="inlineStr">
         <is>
-          <t>From EPGC LLC via mercury.com 3 of 3; Merchant name: Newstar Jewelers</t>
+          <t>From EPGC LLC via mercury.com 3 of 3; Merchant name: Newstar Jewelers; Mercury native: From EPGC LLC via mercury.com 3 of 3 | Send Money transaction initiated on Mercury</t>
         </is>
       </c>
       <c r="L67" s="15" t="inlineStr">
@@ -10965,69 +11000,69 @@
     </row>
     <row r="128"/>
     <row r="129">
-      <c r="A129" s="68" t="inlineStr">
-        <is>
-          <t>2025 Mercury ASK — Fortuna inventory remaining (not in Cost total until object is named)</t>
+      <c r="A129" s="64" t="inlineStr">
+        <is>
+          <t>2025 Mercury Fortuna inventory — Venus + Roman Gold Belt LOCKED; Aug $20k unnamed ASK</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="58" t="inlineStr">
-        <is>
-          <t>Fortuna / Erdal Dere — object TBD</t>
-        </is>
-      </c>
-      <c r="B130" s="58" t="inlineStr">
+      <c r="A130" s="9" t="inlineStr">
+        <is>
+          <t>Bronze head of a goddess, likely Venus — Fortuna inventory</t>
+        </is>
+      </c>
+      <c r="B130" s="9" t="inlineStr">
         <is>
           <t>Mercury 8291</t>
         </is>
       </c>
-      <c r="C130" s="63" t="n">
+      <c r="C130" s="67" t="n">
         <v>20000</v>
       </c>
-      <c r="D130" s="58" t="inlineStr">
+      <c r="D130" s="66" t="inlineStr">
         <is>
           <t>2025-05-09</t>
         </is>
       </c>
-      <c r="I130" s="51" t="inlineStr">
-        <is>
-          <t>ASK: inventory purchase vs other. Do not add to sold Cost until named (avoid double count).</t>
+      <c r="I130" s="8" t="inlineStr">
+        <is>
+          <t>LOCKED 2026-09-20 from Mercury native CSV note. Parked Cost. Not sold 2025 — not in sold-lot Cost. Not tax advice.</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="58" t="inlineStr">
-        <is>
-          <t>Fortuna / Erdal Dere — object TBD</t>
-        </is>
-      </c>
-      <c r="B131" s="58" t="inlineStr">
+      <c r="A131" s="9" t="inlineStr">
+        <is>
+          <t>Roman Gold Belt — Fortuna inventory</t>
+        </is>
+      </c>
+      <c r="B131" s="9" t="inlineStr">
         <is>
           <t>Mercury 8291</t>
         </is>
       </c>
-      <c r="C131" s="63" t="n">
+      <c r="C131" s="67" t="n">
         <v>45000</v>
       </c>
-      <c r="D131" s="58" t="inlineStr">
+      <c r="D131" s="66" t="inlineStr">
         <is>
           <t>2025-07-21</t>
         </is>
       </c>
-      <c r="I131" s="51" t="inlineStr">
-        <is>
-          <t>ASK: inventory purchase vs other. Do not add to sold Cost until named (avoid double count).</t>
+      <c r="I131" s="8" t="inlineStr">
+        <is>
+          <t>LOCKED 2026-09-20 from Mercury native CSV note. Parked Cost. Not sold 2025 — not in sold-lot Cost. Not tax advice.</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="58" t="inlineStr">
-        <is>
-          <t>Fortuna / Erdal Dere — object TBD</t>
-        </is>
-      </c>
-      <c r="B132" s="58" t="inlineStr">
+      <c r="A132" s="19" t="inlineStr">
+        <is>
+          <t>Fortuna / Erdal Dere — object still unnamed (native 8/18 = Monarch 8/15)</t>
+        </is>
+      </c>
+      <c r="B132" s="19" t="inlineStr">
         <is>
           <t>Mercury 8291</t>
         </is>
@@ -11040,20 +11075,20 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="I132" s="51" t="inlineStr">
-        <is>
-          <t>ASK: inventory purchase vs other. Do not add to sold Cost until named (avoid double count).</t>
+      <c r="I132" s="6" t="inlineStr">
+        <is>
+          <t>ASK: same $20,000 as Mercury native 2025-08-18. No object name. Do not add to sold Cost. Not a second unique txn.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="51" t="inlineStr">
         <is>
-          <t>Fortuna remaining 2025 (excl. seals $13,000 already on row 73)</t>
+          <t>Fortuna unnamed remaining 2025 (excl. seals $13,000 + Venus $20,000 + Belt $45,000)</t>
         </is>
       </c>
       <c r="C133" s="63" t="n">
-        <v>85000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="134"/>
@@ -11126,7 +11161,7 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="69" t="inlineStr">
+      <c r="A5" s="68" t="inlineStr">
         <is>
           <t>Coinbase (ACH from Mercury 8291)</t>
         </is>
@@ -11235,16 +11270,16 @@
       <c r="I7" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="70" t="n">
+      <c r="J7" s="69" t="n">
         <v>-9000</v>
       </c>
-      <c r="K7" s="70" t="n">
+      <c r="K7" s="69" t="n">
         <v>-10000</v>
       </c>
-      <c r="L7" s="70" t="n">
+      <c r="L7" s="69" t="n">
         <v>-35000</v>
       </c>
-      <c r="M7" s="70" t="n">
+      <c r="M7" s="69" t="n">
         <v>-5000</v>
       </c>
       <c r="N7" s="60">
@@ -11291,7 +11326,7 @@
       <c r="L8" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="M8" s="70" t="n">
+      <c r="M8" s="69" t="n">
         <v>8000</v>
       </c>
       <c r="N8" s="60">
@@ -11348,7 +11383,7 @@
     </row>
     <row r="10"/>
     <row r="11">
-      <c r="A11" s="71" t="inlineStr">
+      <c r="A11" s="70" t="inlineStr">
         <is>
           <t>2025: funded $59,000.00 / returned $8,000.00 / net $-51,000.00 off the EPGC operating account. Not income, not an expense. Not tax advice.</t>
         </is>
@@ -11476,10 +11511,10 @@
       <c r="E4" s="26" t="n">
         <v>115000</v>
       </c>
-      <c r="F4" s="72" t="n">
+      <c r="F4" s="71" t="n">
         <v>110000</v>
       </c>
-      <c r="G4" s="73" t="n"/>
+      <c r="G4" s="72" t="n"/>
       <c r="H4" s="60" t="n">
         <v>110000</v>
       </c>
@@ -11503,10 +11538,10 @@
         <v>1500</v>
       </c>
       <c r="E5" s="26" t="n"/>
-      <c r="F5" s="72" t="n">
+      <c r="F5" s="71" t="n">
         <v>1500</v>
       </c>
-      <c r="G5" s="73" t="n"/>
+      <c r="G5" s="72" t="n"/>
       <c r="H5" s="60" t="n">
         <v>19500</v>
       </c>
@@ -11524,10 +11559,10 @@
       <c r="C6" s="26" t="n"/>
       <c r="D6" s="26" t="n"/>
       <c r="E6" s="26" t="n"/>
-      <c r="F6" s="72" t="n">
+      <c r="F6" s="71" t="n">
         <v>20000</v>
       </c>
-      <c r="G6" s="73" t="n"/>
+      <c r="G6" s="72" t="n"/>
       <c r="H6" s="60" t="n">
         <v>17000</v>
       </c>
@@ -11553,10 +11588,10 @@
       <c r="E7" s="26" t="n">
         <v>14700</v>
       </c>
-      <c r="F7" s="72" t="n">
+      <c r="F7" s="71" t="n">
         <v>16000</v>
       </c>
-      <c r="G7" s="72" t="n"/>
+      <c r="G7" s="71" t="n"/>
       <c r="H7" s="60" t="n">
         <v>21500</v>
       </c>
@@ -11582,10 +11617,10 @@
       <c r="E8" s="26" t="n">
         <v>54777.25</v>
       </c>
-      <c r="F8" s="72" t="n">
+      <c r="F8" s="71" t="n">
         <v>20000</v>
       </c>
-      <c r="G8" s="73" t="n"/>
+      <c r="G8" s="72" t="n"/>
       <c r="H8" s="60" t="n">
         <v>20000</v>
       </c>
@@ -11609,10 +11644,10 @@
         <v>74000</v>
       </c>
       <c r="E9" s="26" t="n"/>
-      <c r="F9" s="72" t="n">
+      <c r="F9" s="71" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="73" t="n"/>
+      <c r="G9" s="72" t="n"/>
       <c r="H9" s="60" t="n">
         <v>0</v>
       </c>
@@ -11642,19 +11677,19 @@
         <f>SUM(E4:E9)</f>
         <v/>
       </c>
-      <c r="F10" s="72">
+      <c r="F10" s="71">
         <f>SUM(F4:F9)</f>
         <v/>
       </c>
-      <c r="G10" s="72">
+      <c r="G10" s="71">
         <f>SUM(G4:G9)</f>
         <v/>
       </c>
-      <c r="H10" s="72">
+      <c r="H10" s="71">
         <f>SUM(H4:H9)</f>
         <v/>
       </c>
-      <c r="I10" s="72">
+      <c r="I10" s="71">
         <f>SUM(I4:I9)</f>
         <v/>
       </c>
@@ -11664,7 +11699,7 @@
       <c r="B11" s="26" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="71" t="inlineStr">
+      <c r="A12" s="70" t="inlineStr">
         <is>
           <t>2025 Actual: I4 Monarch paycheck cash ≠ W-2 Box 1. I5 216 LTR cash $19,500. I6 524 #2 STR platform net LOCKED. I7 GCM 1099-NEC $21,500. I8 Art net $23,055.06 = MATCHED Mercury deals only (Berk lots $30,000 − $22,944.94 Cost) + seals $1,000 + mosaics $15,000. Excludes Sale 6428 $11,000 until Cost. Excludes Aquinas books $1,000 until Cost. David Aaron $13,595 is EPGC Consultant June (not I8). Erdal/Aysel/EOEB/L5 ASK. Not tax advice.</t>
         </is>
